--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -844,6 +844,7 @@
 Bronshjon
 Dropptaggsvamp
 Mindre märgborre
+Skarp dropptaggsvamp
 Kungsfågel
 Vanlig groda
 Revlummer</t>
@@ -892,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,7 +990,7 @@
         <v>44456</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1091,7 @@
         <v>44664</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,7 +1295,7 @@
         <v>45841</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,7 +1399,7 @@
         <v>45694</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,7 +1498,7 @@
         <v>44110</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,7 +1588,7 @@
         <v>45332</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,7 +1683,7 @@
         <v>45117</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,7 +1786,7 @@
         <v>45591</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,7 +1880,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,7 +1973,7 @@
         <v>44817</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2061,7 +2062,7 @@
         <v>45331</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,7 +2151,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2248,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2343,7 +2344,7 @@
         <v>44068</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2435,7 +2436,7 @@
         <v>45327</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2526,7 +2527,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2618,7 +2619,7 @@
         <v>45827</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2709,7 +2710,7 @@
         <v>45316</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2796,7 +2797,7 @@
         <v>44068</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2887,7 +2888,7 @@
         <v>44091</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2982,7 +2983,7 @@
         <v>45671</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3072,7 +3073,7 @@
         <v>44943</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3158,7 +3159,7 @@
         <v>45790</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3249,7 +3250,7 @@
         <v>44937</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3339,7 +3340,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3429,7 +3430,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3515,7 +3516,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3601,7 +3602,7 @@
         <v>45799</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3687,7 +3688,7 @@
         <v>45671</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3773,7 +3774,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3863,7 +3864,7 @@
         <v>45818</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3949,7 +3950,7 @@
         <v>45820</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4043,7 +4044,7 @@
         <v>44851</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4132,7 +4133,7 @@
         <v>44056</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4222,7 +4223,7 @@
         <v>44257</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4307,7 +4308,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4396,7 +4397,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4485,7 +4486,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4575,7 +4576,7 @@
         <v>45201</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4664,7 +4665,7 @@
         <v>45092</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4753,7 +4754,7 @@
         <v>45777</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4847,7 +4848,7 @@
         <v>45069</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4932,7 +4933,7 @@
         <v>44916</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5021,7 +5022,7 @@
         <v>44965</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5110,7 +5111,7 @@
         <v>45793</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5200,7 +5201,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5289,7 +5290,7 @@
         <v>45117</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5383,7 +5384,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5468,7 +5469,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5558,7 +5559,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5648,7 +5649,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5737,7 +5738,7 @@
         <v>45040</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5822,7 +5823,7 @@
         <v>45827</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5907,7 +5908,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6001,7 +6002,7 @@
         <v>44098</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6058,7 +6059,7 @@
         <v>44096</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6120,7 +6121,7 @@
         <v>44530</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6177,7 +6178,7 @@
         <v>44160</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6234,7 +6235,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6291,7 +6292,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6348,7 +6349,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6405,7 +6406,7 @@
         <v>44077</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6462,7 +6463,7 @@
         <v>44459</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6519,7 +6520,7 @@
         <v>44256</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6576,7 +6577,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6633,7 +6634,7 @@
         <v>44256</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6690,7 +6691,7 @@
         <v>44348</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6747,7 +6748,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6809,7 +6810,7 @@
         <v>44447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6871,7 +6872,7 @@
         <v>44470</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6928,7 +6929,7 @@
         <v>44648</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6985,7 +6986,7 @@
         <v>44648</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7042,7 +7043,7 @@
         <v>44775</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7099,7 +7100,7 @@
         <v>44742</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7161,7 +7162,7 @@
         <v>44755</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7218,7 +7219,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7275,7 +7276,7 @@
         <v>44860</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7332,7 +7333,7 @@
         <v>44169</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7394,7 +7395,7 @@
         <v>44407</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7451,7 +7452,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7508,7 +7509,7 @@
         <v>44636</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7565,7 +7566,7 @@
         <v>44529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7622,7 +7623,7 @@
         <v>44874</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7679,7 +7680,7 @@
         <v>44475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7736,7 +7737,7 @@
         <v>44698</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7798,7 +7799,7 @@
         <v>44827</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7855,7 +7856,7 @@
         <v>44571</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7912,7 +7913,7 @@
         <v>44061</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7969,7 +7970,7 @@
         <v>44648</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8026,7 +8027,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8083,7 +8084,7 @@
         <v>44648</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8140,7 +8141,7 @@
         <v>44067</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8197,7 +8198,7 @@
         <v>44066</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8254,7 +8255,7 @@
         <v>44242</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8311,7 +8312,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8368,7 +8369,7 @@
         <v>44161</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8430,7 +8431,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8487,7 +8488,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8549,7 +8550,7 @@
         <v>44179</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8606,7 +8607,7 @@
         <v>44147</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8663,7 +8664,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8720,7 +8721,7 @@
         <v>44183</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8782,7 +8783,7 @@
         <v>44566</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8839,7 +8840,7 @@
         <v>44368</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8896,7 +8897,7 @@
         <v>44169</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8978,7 +8979,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9035,7 +9036,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9092,7 +9093,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9149,7 +9150,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9211,7 +9212,7 @@
         <v>44407</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9268,7 +9269,7 @@
         <v>44365</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9325,7 +9326,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9382,7 +9383,7 @@
         <v>44224</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9439,7 +9440,7 @@
         <v>44658</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9496,7 +9497,7 @@
         <v>44091</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9553,7 +9554,7 @@
         <v>44466</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9610,7 +9611,7 @@
         <v>44466</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9667,7 +9668,7 @@
         <v>44349</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9724,7 +9725,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9781,7 +9782,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9838,7 +9839,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9895,7 +9896,7 @@
         <v>44419</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9952,7 +9953,7 @@
         <v>44648</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10009,7 +10010,7 @@
         <v>44648</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10066,7 +10067,7 @@
         <v>44648</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10123,7 +10124,7 @@
         <v>44265</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10180,7 +10181,7 @@
         <v>44203</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10237,7 +10238,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10294,7 +10295,7 @@
         <v>44421</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10351,7 +10352,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10408,7 +10409,7 @@
         <v>44085</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10465,7 +10466,7 @@
         <v>44078</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10522,7 +10523,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10579,7 +10580,7 @@
         <v>44644</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10636,7 +10637,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10693,7 +10694,7 @@
         <v>44664</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10755,7 +10756,7 @@
         <v>44698</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10817,7 +10818,7 @@
         <v>44263</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10874,7 +10875,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10936,7 +10937,7 @@
         <v>44389</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10993,7 +10994,7 @@
         <v>44792</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11050,7 +11051,7 @@
         <v>44532</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11107,7 +11108,7 @@
         <v>44491</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11164,7 +11165,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11221,7 +11222,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11278,7 +11279,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11340,7 +11341,7 @@
         <v>44704</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11402,7 +11403,7 @@
         <v>44143</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11464,7 +11465,7 @@
         <v>44418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11521,7 +11522,7 @@
         <v>44397</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11578,7 +11579,7 @@
         <v>44114</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11635,7 +11636,7 @@
         <v>44176</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11697,7 +11698,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11754,7 +11755,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11816,7 +11817,7 @@
         <v>44806</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11873,7 +11874,7 @@
         <v>44407</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11930,7 +11931,7 @@
         <v>44644</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11987,7 +11988,7 @@
         <v>44143</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12044,7 +12045,7 @@
         <v>44131</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12101,7 +12102,7 @@
         <v>44090</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12158,7 +12159,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12215,7 +12216,7 @@
         <v>44160</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12272,7 +12273,7 @@
         <v>44175</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12329,7 +12330,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12386,7 +12387,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12443,7 +12444,7 @@
         <v>44662</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12500,7 +12501,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12562,7 +12563,7 @@
         <v>44095</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12619,7 +12620,7 @@
         <v>44095</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12676,7 +12677,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12733,7 +12734,7 @@
         <v>44183</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12795,7 +12796,7 @@
         <v>44300</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12852,7 +12853,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12914,7 +12915,7 @@
         <v>44517</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12971,7 +12972,7 @@
         <v>44398</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13028,7 +13029,7 @@
         <v>44143</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13090,7 +13091,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13147,7 +13148,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13204,7 +13205,7 @@
         <v>45148</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13266,7 +13267,7 @@
         <v>44383</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13323,7 +13324,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13380,7 +13381,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13437,7 +13438,7 @@
         <v>45188</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13494,7 +13495,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13551,7 +13552,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13613,7 +13614,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13670,7 +13671,7 @@
         <v>45329</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13727,7 +13728,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13784,7 +13785,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13846,7 +13847,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13908,7 +13909,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13965,7 +13966,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14022,7 +14023,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14079,7 +14080,7 @@
         <v>45329</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14136,7 +14137,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14193,7 +14194,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14250,7 +14251,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14307,7 +14308,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14369,7 +14370,7 @@
         <v>45173</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14426,7 +14427,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14483,7 +14484,7 @@
         <v>45727</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14540,7 +14541,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14597,7 +14598,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14654,7 +14655,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14711,7 +14712,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14768,7 +14769,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14825,7 +14826,7 @@
         <v>45189</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14882,7 +14883,7 @@
         <v>45189</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14939,7 +14940,7 @@
         <v>45552</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14996,7 +14997,7 @@
         <v>44789</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15053,7 +15054,7 @@
         <v>45678</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15110,7 +15111,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15167,7 +15168,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15229,7 +15230,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15291,7 +15292,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15348,7 +15349,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15405,7 +15406,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15467,7 +15468,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15524,7 +15525,7 @@
         <v>45148</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15581,7 +15582,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15638,7 +15639,7 @@
         <v>45175</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15695,7 +15696,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15752,7 +15753,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15809,7 +15810,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15871,7 +15872,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15928,7 +15929,7 @@
         <v>45134</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15985,7 +15986,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16042,7 +16043,7 @@
         <v>45418.31987268518</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16104,7 +16105,7 @@
         <v>45097</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16161,7 +16162,7 @@
         <v>44739</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16218,7 +16219,7 @@
         <v>45548</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16275,7 +16276,7 @@
         <v>45362</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16332,7 +16333,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16389,7 +16390,7 @@
         <v>44830</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16446,7 +16447,7 @@
         <v>45762</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16508,7 +16509,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16565,7 +16566,7 @@
         <v>45356</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16622,7 +16623,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16679,7 +16680,7 @@
         <v>44872</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16741,7 +16742,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16798,7 +16799,7 @@
         <v>45632.50675925926</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16860,7 +16861,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16917,7 +16918,7 @@
         <v>44357</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16974,7 +16975,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17036,7 +17037,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17093,7 +17094,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17150,7 +17151,7 @@
         <v>45632.47732638889</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17212,7 +17213,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17269,7 +17270,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17326,7 +17327,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17383,7 +17384,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17445,7 +17446,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17502,7 +17503,7 @@
         <v>44935</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17559,7 +17560,7 @@
         <v>45758</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17621,7 +17622,7 @@
         <v>45429</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17683,7 +17684,7 @@
         <v>44827</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17740,7 +17741,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17797,7 +17798,7 @@
         <v>45331</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17854,7 +17855,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17911,7 +17912,7 @@
         <v>44148</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17968,7 +17969,7 @@
         <v>45757</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18030,7 +18031,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18087,7 +18088,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18144,7 +18145,7 @@
         <v>45223</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18201,7 +18202,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18258,7 +18259,7 @@
         <v>44887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18315,7 +18316,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18372,7 +18373,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18434,7 +18435,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18491,7 +18492,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18548,7 +18549,7 @@
         <v>45758</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18610,7 +18611,7 @@
         <v>45758</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18672,7 +18673,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18729,7 +18730,7 @@
         <v>44797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18786,7 +18787,7 @@
         <v>45105</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18843,7 +18844,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18900,7 +18901,7 @@
         <v>44497</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18962,7 +18963,7 @@
         <v>44412</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19019,7 +19020,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19076,7 +19077,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19133,7 +19134,7 @@
         <v>45040</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19190,7 +19191,7 @@
         <v>44873</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19247,7 +19248,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19304,7 +19305,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19361,7 +19362,7 @@
         <v>44824</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19418,7 +19419,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19475,7 +19476,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19537,7 +19538,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19594,7 +19595,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19651,7 +19652,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19708,7 +19709,7 @@
         <v>44804</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19770,7 +19771,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19827,7 +19828,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19884,7 +19885,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19941,7 +19942,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19998,7 +19999,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20055,7 +20056,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20112,7 +20113,7 @@
         <v>44937</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20169,7 +20170,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20226,7 +20227,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20283,7 +20284,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20340,7 +20341,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20397,7 +20398,7 @@
         <v>45397</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20454,7 +20455,7 @@
         <v>45579</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20511,7 +20512,7 @@
         <v>45323</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20568,7 +20569,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20625,7 +20626,7 @@
         <v>44889</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20682,7 +20683,7 @@
         <v>45054</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20739,7 +20740,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20796,7 +20797,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20853,7 +20854,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20910,7 +20911,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20967,7 +20968,7 @@
         <v>45258</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21024,7 +21025,7 @@
         <v>45203</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21081,7 +21082,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21138,7 +21139,7 @@
         <v>45751</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21200,7 +21201,7 @@
         <v>45751</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21262,7 +21263,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21324,7 +21325,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21386,7 +21387,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21443,7 +21444,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21500,7 +21501,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21557,7 +21558,7 @@
         <v>45771</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21619,7 +21620,7 @@
         <v>45250</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21676,7 +21677,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21733,7 +21734,7 @@
         <v>45632.4877662037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21795,7 +21796,7 @@
         <v>45034</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21852,7 +21853,7 @@
         <v>45250</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21909,7 +21910,7 @@
         <v>45250</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21966,7 +21967,7 @@
         <v>45632.46594907407</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22028,7 +22029,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22085,7 +22086,7 @@
         <v>44949</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22142,7 +22143,7 @@
         <v>45741</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22199,7 +22200,7 @@
         <v>45693</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22276,7 +22277,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22333,7 +22334,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22390,7 +22391,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22447,7 +22448,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22504,7 +22505,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22561,7 +22562,7 @@
         <v>45329</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22618,7 +22619,7 @@
         <v>45113</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22675,7 +22676,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22732,7 +22733,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22789,7 +22790,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22846,7 +22847,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22908,7 +22909,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22965,7 +22966,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23022,7 +23023,7 @@
         <v>45513</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23079,7 +23080,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23136,7 +23137,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23198,7 +23199,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23255,7 +23256,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23312,7 +23313,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23369,7 +23370,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23426,7 +23427,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23488,7 +23489,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23545,7 +23546,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23602,7 +23603,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23664,7 +23665,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23726,7 +23727,7 @@
         <v>45189</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23783,7 +23784,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23840,7 +23841,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23897,7 +23898,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23954,7 +23955,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24011,7 +24012,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24068,7 +24069,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24125,7 +24126,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24182,7 +24183,7 @@
         <v>45777</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24244,7 +24245,7 @@
         <v>44964</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24301,7 +24302,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24358,7 +24359,7 @@
         <v>45329</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24415,7 +24416,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24472,7 +24473,7 @@
         <v>44909</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24529,7 +24530,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24586,7 +24587,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24643,7 +24644,7 @@
         <v>45343</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24700,7 +24701,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24757,7 +24758,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24814,7 +24815,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24871,7 +24872,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24928,7 +24929,7 @@
         <v>45560</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24990,7 +24991,7 @@
         <v>45187</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25047,7 +25048,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25109,7 +25110,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25166,7 +25167,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25223,7 +25224,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25280,7 +25281,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25337,7 +25338,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25394,7 +25395,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25451,7 +25452,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25508,7 +25509,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25565,7 +25566,7 @@
         <v>44162</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25627,7 +25628,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25684,7 +25685,7 @@
         <v>45405</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25741,7 +25742,7 @@
         <v>45398.68</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25798,7 +25799,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25855,7 +25856,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25917,7 +25918,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25974,7 +25975,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26031,7 +26032,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26088,7 +26089,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26145,7 +26146,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26207,7 +26208,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26269,7 +26270,7 @@
         <v>45442.51335648148</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26331,7 +26332,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26388,7 +26389,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26450,7 +26451,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26507,7 +26508,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26564,7 +26565,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26626,7 +26627,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26688,7 +26689,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26750,7 +26751,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26812,7 +26813,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26869,7 +26870,7 @@
         <v>45741</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26926,7 +26927,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26983,7 +26984,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27040,7 +27041,7 @@
         <v>45476</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27097,7 +27098,7 @@
         <v>44882</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27154,7 +27155,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27211,7 +27212,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27268,7 +27269,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27325,7 +27326,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27382,7 +27383,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27439,7 +27440,7 @@
         <v>45785</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27501,7 +27502,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27558,7 +27559,7 @@
         <v>45350</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27615,7 +27616,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27672,7 +27673,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27734,7 +27735,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27796,7 +27797,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27853,7 +27854,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27915,7 +27916,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27972,7 +27973,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28029,7 +28030,7 @@
         <v>45198</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28086,7 +28087,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28143,7 +28144,7 @@
         <v>45611</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28200,7 +28201,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28262,7 +28263,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28319,7 +28320,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28381,7 +28382,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28438,7 +28439,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28500,7 +28501,7 @@
         <v>44910</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28557,7 +28558,7 @@
         <v>44382</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28614,7 +28615,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28671,7 +28672,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28728,7 +28729,7 @@
         <v>45330</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28785,7 +28786,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28842,7 +28843,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28899,7 +28900,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28961,7 +28962,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29018,7 +29019,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29075,7 +29076,7 @@
         <v>44558</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29132,7 +29133,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29189,7 +29190,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29251,7 +29252,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29308,7 +29309,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29370,7 +29371,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29427,7 +29428,7 @@
         <v>45792</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29489,7 +29490,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29546,7 +29547,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29603,7 +29604,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29665,7 +29666,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29727,7 +29728,7 @@
         <v>45634</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29784,7 +29785,7 @@
         <v>44644</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29841,7 +29842,7 @@
         <v>45428</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29903,7 +29904,7 @@
         <v>44714</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29965,7 +29966,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30027,7 +30028,7 @@
         <v>45535</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30084,7 +30085,7 @@
         <v>45252</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30141,7 +30142,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30198,7 +30199,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30255,7 +30256,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30317,7 +30318,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30374,7 +30375,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30436,7 +30437,7 @@
         <v>45838</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30493,7 +30494,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30550,7 +30551,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30607,7 +30608,7 @@
         <v>44397</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30664,7 +30665,7 @@
         <v>45072</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30721,7 +30722,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30783,7 +30784,7 @@
         <v>44972</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30840,7 +30841,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30897,7 +30898,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30954,7 +30955,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31011,7 +31012,7 @@
         <v>45835</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31068,7 +31069,7 @@
         <v>45341</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31125,7 +31126,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31182,7 +31183,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31239,7 +31240,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31301,7 +31302,7 @@
         <v>45629.66504629629</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31363,7 +31364,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31425,7 +31426,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31482,7 +31483,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31539,7 +31540,7 @@
         <v>45632.47288194444</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31601,7 +31602,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31658,7 +31659,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31715,7 +31716,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31772,7 +31773,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31829,7 +31830,7 @@
         <v>45678</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31886,7 +31887,7 @@
         <v>45148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31943,7 +31944,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32005,7 +32006,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32062,7 +32063,7 @@
         <v>45224</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32119,7 +32120,7 @@
         <v>45836</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32176,7 +32177,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32238,7 +32239,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32295,7 +32296,7 @@
         <v>45611</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32352,7 +32353,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32409,7 +32410,7 @@
         <v>45189</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32466,7 +32467,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32523,7 +32524,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32580,7 +32581,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32642,7 +32643,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32699,7 +32700,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32756,7 +32757,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32818,7 +32819,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32875,7 +32876,7 @@
         <v>45435</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32932,7 +32933,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32989,7 +32990,7 @@
         <v>44648</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33046,7 +33047,7 @@
         <v>45838</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33103,7 +33104,7 @@
         <v>45201</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33160,7 +33161,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33217,7 +33218,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33274,7 +33275,7 @@
         <v>44110</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33331,7 +33332,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33388,7 +33389,7 @@
         <v>45635</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33445,7 +33446,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33502,7 +33503,7 @@
         <v>44945</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33559,7 +33560,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33616,7 +33617,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33673,7 +33674,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33735,7 +33736,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33797,7 +33798,7 @@
         <v>45840</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33854,7 +33855,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33916,7 +33917,7 @@
         <v>45798</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33973,7 +33974,7 @@
         <v>45798</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34030,7 +34031,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34087,7 +34088,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34149,7 +34150,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34206,7 +34207,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34263,7 +34264,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34320,7 +34321,7 @@
         <v>45797</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34382,7 +34383,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34444,7 +34445,7 @@
         <v>45840</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34506,7 +34507,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34563,7 +34564,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34620,7 +34621,7 @@
         <v>45453</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34682,7 +34683,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34739,7 +34740,7 @@
         <v>45232</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34796,7 +34797,7 @@
         <v>45741.67026620371</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34858,7 +34859,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34915,7 +34916,7 @@
         <v>45274</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34972,7 +34973,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35029,7 +35030,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35086,7 +35087,7 @@
         <v>45800</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35148,7 +35149,7 @@
         <v>45723</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35205,7 +35206,7 @@
         <v>44242</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35262,7 +35263,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35319,7 +35320,7 @@
         <v>45841</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35381,7 +35382,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35438,7 +35439,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35495,7 +35496,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35557,7 +35558,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35614,7 +35615,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35676,7 +35677,7 @@
         <v>45839</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35733,7 +35734,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35790,7 +35791,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35847,7 +35848,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35904,7 +35905,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35961,7 +35962,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36018,7 +36019,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36100,7 +36101,7 @@
         <v>44697</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36157,7 +36158,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36214,7 +36215,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36271,7 +36272,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36333,7 +36334,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36395,7 +36396,7 @@
         <v>45607</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36457,7 +36458,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36519,7 +36520,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36576,7 +36577,7 @@
         <v>45607</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36638,7 +36639,7 @@
         <v>45148</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36700,7 +36701,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36757,7 +36758,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36814,7 +36815,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36871,7 +36872,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36933,7 +36934,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36990,7 +36991,7 @@
         <v>45238</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37047,7 +37048,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37109,7 +37110,7 @@
         <v>45632.49576388889</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37171,7 +37172,7 @@
         <v>45800</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37228,7 +37229,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37285,7 +37286,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37342,7 +37343,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37399,7 +37400,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37461,7 +37462,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37518,7 +37519,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37575,7 +37576,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37632,7 +37633,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37709,7 +37710,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37766,7 +37767,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37823,7 +37824,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37880,7 +37881,7 @@
         <v>44342</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37937,7 +37938,7 @@
         <v>44742</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37999,7 +38000,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38061,7 +38062,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38118,7 +38119,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38175,7 +38176,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38232,7 +38233,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38289,7 +38290,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38346,7 +38347,7 @@
         <v>45607</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38408,7 +38409,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38465,7 +38466,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38527,7 +38528,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38584,7 +38585,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38641,7 +38642,7 @@
         <v>45807.565</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38698,7 +38699,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38760,7 +38761,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38817,7 +38818,7 @@
         <v>45751</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38879,7 +38880,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38936,7 +38937,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38998,7 +38999,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39055,7 +39056,7 @@
         <v>45707.58730324074</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39112,7 +39113,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39169,7 +39170,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39226,7 +39227,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39283,7 +39284,7 @@
         <v>45723</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39340,7 +39341,7 @@
         <v>45222</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39397,7 +39398,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39454,7 +39455,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39511,7 +39512,7 @@
         <v>45845</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39568,7 +39569,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39625,7 +39626,7 @@
         <v>45810</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39682,7 +39683,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39739,7 +39740,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39801,7 +39802,7 @@
         <v>45670</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39858,7 +39859,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39915,7 +39916,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39972,7 +39973,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40029,7 +40030,7 @@
         <v>45572.62424768518</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40086,7 +40087,7 @@
         <v>45616</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40143,7 +40144,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40205,7 +40206,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40262,7 +40263,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40319,7 +40320,7 @@
         <v>44228</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40376,7 +40377,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40433,7 +40434,7 @@
         <v>45401.36445601852</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40490,7 +40491,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40552,7 +40553,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40609,7 +40610,7 @@
         <v>44792</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40666,7 +40667,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40728,7 +40729,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40785,7 +40786,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40842,7 +40843,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40899,7 +40900,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40956,7 +40957,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41013,7 +41014,7 @@
         <v>44973</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41070,7 +41071,7 @@
         <v>45761</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41132,7 +41133,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41194,7 +41195,7 @@
         <v>45706</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41256,7 +41257,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41313,7 +41314,7 @@
         <v>45744.6449074074</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41370,7 +41371,7 @@
         <v>45841</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41432,7 +41433,7 @@
         <v>45813</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41489,7 +41490,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41546,7 +41547,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41608,7 +41609,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41665,7 +41666,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41722,7 +41723,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41779,7 +41780,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41836,7 +41837,7 @@
         <v>45756</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41893,7 +41894,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41950,7 +41951,7 @@
         <v>45463</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42007,7 +42008,7 @@
         <v>45671</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42064,7 +42065,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42121,7 +42122,7 @@
         <v>45356</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42178,7 +42179,7 @@
         <v>44725</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42240,7 +42241,7 @@
         <v>45769.63487268519</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42297,7 +42298,7 @@
         <v>45068</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42354,7 +42355,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42411,7 +42412,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42468,7 +42469,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42525,7 +42526,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42582,7 +42583,7 @@
         <v>45819</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42644,7 +42645,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42706,7 +42707,7 @@
         <v>45820</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42763,7 +42764,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42820,7 +42821,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42877,7 +42878,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42934,7 +42935,7 @@
         <v>45306</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42991,7 +42992,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43048,7 +43049,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43105,7 +43106,7 @@
         <v>44060</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43162,7 +43163,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43219,7 +43220,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43276,7 +43277,7 @@
         <v>44397</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43333,7 +43334,7 @@
         <v>44755</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43390,7 +43391,7 @@
         <v>44755</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43447,7 +43448,7 @@
         <v>45226</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43504,7 +43505,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43561,7 +43562,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43618,7 +43619,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43675,7 +43676,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43737,7 +43738,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43799,7 +43800,7 @@
         <v>45274</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43856,7 +43857,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43913,7 +43914,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43970,7 +43971,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44032,7 +44033,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44094,7 +44095,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44151,7 +44152,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44208,7 +44209,7 @@
         <v>45706</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44270,7 +44271,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44332,7 +44333,7 @@
         <v>45028</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44389,7 +44390,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44471,7 +44472,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44528,7 +44529,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44585,7 +44586,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44642,7 +44643,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44699,7 +44700,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44756,7 +44757,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44813,7 +44814,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44870,7 +44871,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44932,7 +44933,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44989,7 +44990,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45046,7 +45047,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45103,7 +45104,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45160,7 +45161,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45217,7 +45218,7 @@
         <v>44792</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45274,7 +45275,7 @@
         <v>44792</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45331,7 +45332,7 @@
         <v>44117</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45393,7 +45394,7 @@
         <v>45160</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45450,7 +45451,7 @@
         <v>45831</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45507,7 +45508,7 @@
         <v>45198</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45564,7 +45565,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45626,7 +45627,7 @@
         <v>45677</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45683,7 +45684,7 @@
         <v>45831</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45740,7 +45741,7 @@
         <v>45832</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45802,7 +45803,7 @@
         <v>45761</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45864,7 +45865,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45926,7 +45927,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45988,7 +45989,7 @@
         <v>45832</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46050,7 +46051,7 @@
         <v>45673.67585648148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46107,7 +46108,7 @@
         <v>45196</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46164,7 +46165,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46221,7 +46222,7 @@
         <v>45832</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46278,7 +46279,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46335,7 +46336,7 @@
         <v>45336</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46392,7 +46393,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46449,7 +46450,7 @@
         <v>45741.42721064815</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46506,7 +46507,7 @@
         <v>45874</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46563,7 +46564,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46625,7 +46626,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46682,7 +46683,7 @@
         <v>45833</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46744,7 +46745,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46801,7 +46802,7 @@
         <v>45833</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46863,7 +46864,7 @@
         <v>45761</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46925,7 +46926,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46987,7 +46988,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47049,7 +47050,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47106,7 +47107,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47163,7 +47164,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47220,7 +47221,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47277,7 +47278,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47334,7 +47335,7 @@
         <v>45267</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47391,7 +47392,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47448,7 +47449,7 @@
         <v>45400.62608796296</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47505,7 +47506,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47562,7 +47563,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47619,7 +47620,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47676,7 +47677,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47733,7 +47734,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47790,7 +47791,7 @@
         <v>44417</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47847,7 +47848,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47909,7 +47910,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47966,7 +47967,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48028,7 +48029,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48085,7 +48086,7 @@
         <v>44960</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48142,7 +48143,7 @@
         <v>45419.72936342593</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48199,7 +48200,7 @@
         <v>44802</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48256,7 +48257,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48313,7 +48314,7 @@
         <v>45281</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48370,7 +48371,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48427,7 +48428,7 @@
         <v>45579</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48484,7 +48485,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48546,7 +48547,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48608,7 +48609,7 @@
         <v>45180</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48665,7 +48666,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48727,7 +48728,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48784,7 +48785,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48846,7 +48847,7 @@
         <v>44658</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48903,7 +48904,7 @@
         <v>45428</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48965,7 +48966,7 @@
         <v>45428</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49027,7 +49028,7 @@
         <v>44834</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49084,7 +49085,7 @@
         <v>44384</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49146,7 +49147,7 @@
         <v>44987</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49203,7 +49204,7 @@
         <v>44256</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49260,7 +49261,7 @@
         <v>45099</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49317,7 +49318,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49379,7 +49380,7 @@
         <v>44314</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49441,7 +49442,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49503,7 +49504,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49560,7 +49561,7 @@
         <v>45678</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49617,7 +49618,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49674,7 +49675,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49736,7 +49737,7 @@
         <v>44466</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49793,7 +49794,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49850,7 +49851,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49907,7 +49908,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49964,7 +49965,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50021,7 +50022,7 @@
         <v>45433.60685185185</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50078,7 +50079,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50135,7 +50136,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50192,7 +50193,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50249,7 +50250,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50306,7 +50307,7 @@
         <v>45590.39892361111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50363,7 +50364,7 @@
         <v>45195</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50420,7 +50421,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50477,7 +50478,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44664</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44456</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45694</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45841</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>45332</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45117</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44110</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45591</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44817</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45331</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>44068</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45827</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45316</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45327</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>44068</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>44091</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45790</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45799</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44916</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45818</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45820</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>44937</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45671</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44943</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45671</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>44851</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44257</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>45777</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45793</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>45117</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>45069</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45827</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44965</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>45040</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45201</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45092</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>44098</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44096</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>44160</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44530</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44459</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44256</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44256</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44348</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44447</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44470</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44648</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44648</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44742</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44775</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44755</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44169</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44860</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>44407</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44636</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44475</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>44874</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44698</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44827</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>44571</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44061</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44067</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44648</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>44648</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44066</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44242</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44161</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>44179</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44147</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44183</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44566</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44368</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>44169</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44407</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>44365</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>44224</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44658</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44091</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44466</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44466</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>44349</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>44419</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>44648</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>44648</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>44648</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>44265</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>44203</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>44421</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44664</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>44698</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44263</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44792</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>44389</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44491</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44532</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>44704</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44397</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44143</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44418</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44176</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44114</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44806</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44407</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44143</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44131</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44090</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44175</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44662</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>44160</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>44095</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44095</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>44183</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44300</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>44517</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44143</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44398</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44085</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>44078</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44383</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44644</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>45741</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45034</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45693</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45329</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>45418.31987268518</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45097</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45250</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45250</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45362</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>44830</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45356</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45329</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44872</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44357</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45113</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44935</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45513</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45429</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>44827</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45552</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45223</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44789</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45777</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45343</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45187</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45560</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45398.68</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45476</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45785</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>45350</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45330</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45611</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45792</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45535</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>44558</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>44797</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44644</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45435</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>44581</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45635</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>45072</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45798</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45798</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45797</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45341</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45632.47288194444</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44497</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45800</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45723</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45224</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45611</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45201</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44110</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45800</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>44937</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45397</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45323</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45232</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>44889</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45807.565</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>44697</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>45148</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45845</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>44949</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45810</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45238</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45632.49576388889</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45572.62424768518</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>44342</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>44742</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45813</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45189</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>45751</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44964</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45329</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44909</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45222</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>44162</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45819</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45820</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44228</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45401.36445601852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>44792</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45405</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45761</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45744.6449074074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45442.51335648148</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45756</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45741</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44882</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45463</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45671</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45356</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44725</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45769.63487268519</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>45198</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45831</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45831</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45832</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44910</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44382</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45832</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45306</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45832</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>45874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44755</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44755</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45226</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>45833</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45833</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45274</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45835</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44792</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44792</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45836</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45198</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45838</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45761</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>45673.67585648148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45838</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45196</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45840</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45634</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45428</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44714</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45252</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45840</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45336</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35592,7 +35592,7 @@
         <v>45839</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45741.42721064815</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>44397</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>44972</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45761</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45877.34554398148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45629.66504629629</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45678</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>45841</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45267</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>45841</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45400.62608796296</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45189</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44648</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44417</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44945</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45453</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>45741.67026620371</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45274</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44960</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44242</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>45419.72936342593</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44802</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45281</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45579</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45607</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45607</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45180</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45001</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44658</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45607</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45428</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45428</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>45707.58730324074</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>44384</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>44987</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>44256</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45159</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>45099</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>45670</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45616</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44314</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45678</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44973</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44466</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45706</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45433.60685185185</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45068</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>45590.39892361111</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>45195</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44060</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44397</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45182</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45706</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45028</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45188</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>44826</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44117</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
         <v>45160</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>45677</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45189</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>45189</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45678</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45148</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>45329</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45727</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
         <v>44739</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>45548</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45762</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45632.50675925926</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45175</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>45758</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>45331</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45134</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>45632.47732638889</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>44824</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>44148</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>45757</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45579</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>44887</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45758</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>45758</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49104,7 +49104,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>45258</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44412</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45203</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45040</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>44873</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>44804</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49912,7 +49912,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50083,7 +50083,7 @@
         <v>45771</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50145,7 +50145,7 @@
         <v>45250</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>45054</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>45632.4877662037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45751</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45751</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45632.46594907407</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44664</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44456</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45694</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45841</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>45332</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45117</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44110</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45591</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44817</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45331</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>44068</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45827</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45316</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45327</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>44068</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>44091</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45790</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45799</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44916</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45818</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45820</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>44937</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45671</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44943</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45671</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>44851</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44257</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>45777</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45793</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>45117</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>45069</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45827</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44965</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>45040</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45201</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45092</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>44098</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44096</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>44160</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44530</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44459</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44256</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44256</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44348</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44447</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44470</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44648</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44648</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44742</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44775</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44755</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44169</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44860</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>44407</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44636</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44475</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>44874</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44698</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44827</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>44571</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44061</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44067</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44648</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>44648</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44066</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44242</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44161</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>44179</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44147</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44183</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44566</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44368</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>44169</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44407</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>44365</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>44224</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44658</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44091</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44466</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44466</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>44349</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>44419</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>44648</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>44648</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>44648</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>44265</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>44203</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>44421</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44664</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>44698</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44263</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44792</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>44389</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44491</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44532</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>44704</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44397</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44143</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44418</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44176</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44114</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44806</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44407</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44143</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44131</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44090</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44175</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44662</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>44160</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>44095</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44095</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>44183</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44300</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>44517</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44143</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44398</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44085</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>44078</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44383</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44644</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>45741</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45034</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45693</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45329</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>45418.31987268518</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45097</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45250</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45250</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45362</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>44830</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45356</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45329</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44872</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44357</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45113</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44935</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45513</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45429</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>44827</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45552</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45223</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44789</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45777</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45343</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45187</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45560</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45398.68</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45476</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45785</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>45350</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45330</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45611</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45792</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45535</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>44558</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>44797</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44644</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45435</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>44581</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45635</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>45072</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45798</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45798</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45797</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45341</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45632.47288194444</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44497</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45800</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45723</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45224</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45611</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45201</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44110</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45800</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>44937</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45397</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45323</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45232</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>44889</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45807.565</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>44697</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>45148</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45845</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>44949</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45810</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45238</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45632.49576388889</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45572.62424768518</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>44342</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>44742</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45813</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45189</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>45751</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44964</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45329</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44909</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45222</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>44162</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45819</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45820</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44228</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45401.36445601852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>44792</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45405</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45761</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45744.6449074074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45442.51335648148</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45756</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45741</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44882</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45463</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45671</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45356</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44725</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45769.63487268519</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>45198</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45831</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45831</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45832</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44910</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44382</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45832</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45306</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45832</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>45874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44755</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44755</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45226</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>45833</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45833</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45274</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45835</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44792</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44792</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45836</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45198</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45838</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45761</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>45673.67585648148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45838</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45196</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45840</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45634</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45428</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44714</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45252</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45840</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45336</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35592,7 +35592,7 @@
         <v>45839</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45741.42721064815</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>44397</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>44972</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45761</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45877.34554398148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45629.66504629629</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45678</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>45841</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45267</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>45841</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45400.62608796296</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45189</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44648</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44417</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44945</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45453</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>45741.67026620371</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45274</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44960</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44242</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>45419.72936342593</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44802</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45281</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45579</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45607</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45607</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45180</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45001</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44658</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45607</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45428</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45428</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>45707.58730324074</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>44384</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>44987</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>44256</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45159</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>45099</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>45670</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45616</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44314</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45678</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44973</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44466</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45706</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45433.60685185185</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45068</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>45590.39892361111</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>45195</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44060</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44397</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45182</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45706</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45028</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45188</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>44826</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44117</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
         <v>45160</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>45677</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45189</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>45189</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45678</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45148</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>45329</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45727</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
         <v>44739</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>45548</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45762</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45632.50675925926</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45175</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>45758</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>45331</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45134</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>45632.47732638889</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>44824</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>44148</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>45757</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45579</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>44887</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45758</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>45758</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49104,7 +49104,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>45258</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44412</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45203</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45040</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>44873</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>44804</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49912,7 +49912,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50083,7 +50083,7 @@
         <v>45771</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50145,7 +50145,7 @@
         <v>45250</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>45054</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>45632.4877662037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45751</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45751</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45632.46594907407</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44456</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>44664</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45694</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45841</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>45591</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45332</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>44110</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44817</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45331</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>44068</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45327</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45827</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>45316</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>44068</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>44091</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45671</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44937</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44943</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45790</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44916</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45671</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45818</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45820</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>44851</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45201</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45793</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45069</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>45117</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45040</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45827</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44965</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45092</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>44098</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44096</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44160</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>44077</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>44256</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44459</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44256</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44348</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44447</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44775</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44648</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44648</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44470</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44742</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44755</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44169</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44407</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44636</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44698</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44529</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44874</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44827</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44571</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44067</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44648</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44648</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44648</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44066</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44242</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44161</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44860</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44179</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44147</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44183</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44566</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44368</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>44169</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44365</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44407</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44224</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44658</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44091</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44466</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44466</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44349</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44648</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44648</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44265</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44203</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44421</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44085</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44078</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44644</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44263</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>44664</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44698</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44389</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44532</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44491</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44792</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44704</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44143</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>44418</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>44176</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>44397</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44806</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44114</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44644</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>44143</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44131</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44407</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>44175</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>44160</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44183</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>44090</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>44662</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45028</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44300</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>44095</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44095</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44517</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>45418.31987268518</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45757</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44398</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45634</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44792</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44792</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44143</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>45175</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45072</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45250</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45189</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45189</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>44558</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>44466</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44910</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45336</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>44949</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45189</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44755</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45180</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45173</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45329</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45706</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44314</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>44412</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45419.72936342593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45134</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44826</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44889</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45744.6449074074</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45397</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44804</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45761</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45769.63487268519</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45590.39892361111</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>44755</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45453</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45196</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45400.62608796296</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45751</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45188</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>44648</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45513</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45040</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45727</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45341</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45252</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44935</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>44497</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45632.49576388889</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45182</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45579</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45362</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45099</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44834</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44960</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45777</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45678</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44945</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45187</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45343</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45611</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45476</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45548</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45785</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45267</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45198</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45350</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45330</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44228</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44658</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45001</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44909</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44972</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>44397</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>45203</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45771</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45433.60685185185</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45678</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45034</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45258</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45535</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45201</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45741</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>45159</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44887</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45792</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45222</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45442.51335648148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>45428</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45428</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>44110</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44581</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45611</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45306</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45148</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45463</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45635</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45797</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>45226</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45274</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45673.67585648148</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44872</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45435</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>45632.47288194444</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44256</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45798</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45798</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45723</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>44384</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45800</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45677</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45671</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>44342</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45800</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45401.36445601852</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>45097</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45807.565</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>44882</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44242</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>45572.62424768518</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>44937</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>45189</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45232</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45238</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45148</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>45756</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45429</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45810</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45616</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36438,7 +36438,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45579</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45813</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>44964</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>44789</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45198</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>45160</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45629.66504629629</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44382</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45250</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45250</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>44987</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45223</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45105</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44714</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45113</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45819</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45706</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45820</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45356</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45281</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44697</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45751</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45632.50675925926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45607</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>45428</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>44830</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45758</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45329</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41889,7 +41889,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45831</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>45831</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>45607</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45331</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45398.68</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>44792</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45832</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45054</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45833</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>45874</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>45832</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45832</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45833</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>45835</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>45607</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>45560</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45670</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45329</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         <v>44802</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45838</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45838</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45836</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45839</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>44873</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45840</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>44725</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44162</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45841</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>45758</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>45840</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45841</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45632.4877662037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>45224</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45329</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45887.38813657407</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45845</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45632.46594907407</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45405</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>44117</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>44827</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45877.34554398148</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>44417</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>45552</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>45887.63130787037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45723</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>45751</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45889.45498842592</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45888</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>45693</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45889.39368055556</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>45889.63824074074</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48396,7 +48396,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>45323</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>45888.66804398148</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>45888.6709375</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45888.34069444444</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48743,7 +48743,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45274</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48924,7 +48924,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45890.60149305555</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45678</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45148</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45762</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>44644</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45761</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>45761</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>44797</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>44742</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>45741</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>44397</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50441,7 +50441,7 @@
         <v>45758</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>44739</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50560,7 +50560,7 @@
         <v>44824</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45632.47732638889</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44456</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>44664</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45694</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45841</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>45591</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45332</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>44110</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44817</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45331</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>44068</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45327</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45827</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>45316</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>44068</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>44091</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45671</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44937</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44943</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45790</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44916</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45671</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45818</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45820</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>44851</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45201</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45793</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45069</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>45117</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45040</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45827</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44965</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45092</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>44098</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44096</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44160</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>44077</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>44256</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44459</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44256</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44348</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44447</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44775</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44648</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44648</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44470</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44742</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44755</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44169</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44407</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44636</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44698</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44529</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44874</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44827</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44571</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44067</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44648</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44648</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44648</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44066</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44242</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44161</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44860</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44179</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44147</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44183</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44566</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44368</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>44169</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44365</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44407</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44224</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44658</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44091</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44466</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44466</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44349</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44648</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44648</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44265</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44203</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44421</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44085</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44078</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44644</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44263</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>44664</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44698</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44389</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44532</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44491</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44792</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44704</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44143</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>44418</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>44176</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>44397</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44806</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44114</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44644</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>44143</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44131</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44407</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>44175</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>44160</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44183</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>44090</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>44662</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45028</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44300</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>44095</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44095</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44517</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>45418.31987268518</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45757</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44398</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45634</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44792</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44792</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44143</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>45175</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45072</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45250</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45189</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45189</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>44558</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>44466</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44910</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45336</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>44949</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45189</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44755</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45180</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45173</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45329</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45706</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44314</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>44412</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45419.72936342593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45134</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44826</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44889</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45744.6449074074</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45397</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44804</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45761</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45769.63487268519</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45590.39892361111</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>44755</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45453</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45196</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45400.62608796296</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45751</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45188</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>44648</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45513</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45040</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45727</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45341</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45252</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44935</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>44497</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45632.49576388889</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45182</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45579</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45362</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45099</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44834</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44960</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45777</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45678</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44945</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45187</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45343</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45611</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45476</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45548</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45785</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45267</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45198</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45350</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45330</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44228</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44658</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45001</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44909</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44972</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>44397</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>45203</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45771</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45433.60685185185</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45678</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45034</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45258</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45535</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45201</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45741</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>45159</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44887</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45792</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45222</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45442.51335648148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>45428</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45428</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>44110</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44581</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45611</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45306</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45148</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45463</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45635</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45797</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>45226</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45274</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45673.67585648148</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44872</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45435</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>45632.47288194444</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44256</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45798</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45798</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45723</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>44384</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45800</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45677</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45671</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>44342</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45800</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45401.36445601852</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>45097</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45807.565</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>44882</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44242</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>45572.62424768518</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>44937</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>45189</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45232</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45238</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45148</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>45756</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45429</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45810</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45616</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36438,7 +36438,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45579</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45813</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>44964</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>44789</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45198</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>45160</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45629.66504629629</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44382</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45250</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45250</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>44987</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45223</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45105</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44714</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45113</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45819</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45706</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45820</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45356</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45281</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44697</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45751</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45632.50675925926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45607</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>45428</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>44830</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45758</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45329</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41889,7 +41889,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45831</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>45831</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>45607</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45331</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45398.68</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>44792</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45832</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45054</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45833</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>45874</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>45832</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45832</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45833</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>45835</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>45607</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>45560</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45670</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45329</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         <v>44802</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45838</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45838</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45836</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45839</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>44873</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45840</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>44725</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44162</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45841</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>45758</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>45840</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45841</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45632.4877662037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>45224</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45329</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45887.38813657407</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45845</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45632.46594907407</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45405</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>44117</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>44827</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45877.34554398148</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>44417</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>45552</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>45887.63130787037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45723</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>45751</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45889.45498842592</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45888</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>45693</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45889.39368055556</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>45889.63824074074</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48396,7 +48396,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>45323</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>45888.66804398148</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>45888.6709375</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45888.34069444444</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48743,7 +48743,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45274</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48924,7 +48924,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45890.60149305555</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45678</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45148</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45762</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>44644</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45761</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>45761</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>44797</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>44742</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>45741</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>44397</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50441,7 +50441,7 @@
         <v>45758</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>44739</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50560,7 +50560,7 @@
         <v>44824</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45632.47732638889</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44664</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44456</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45694</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45841</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45332</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45117</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44110</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>45591</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44817</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45331</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>45827</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>45316</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45327</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>44091</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>45790</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44916</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45818</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44937</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45671</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45820</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45671</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>44943</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44851</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44257</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>45793</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45069</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44965</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>45117</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45827</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>45040</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45898.40256944444</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45201</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45092</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44098</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44096</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44160</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44077</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44459</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>44256</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44256</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44447</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>44470</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44775</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>44648</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44648</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44742</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44755</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44169</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>44860</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44407</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44636</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44698</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44529</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44475</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44874</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>44827</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44571</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44648</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44648</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44648</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44242</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44161</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>44179</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44147</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44183</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44169</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>44365</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44224</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44658</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44091</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44466</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>44466</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>44349</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>44419</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>44648</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44648</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44648</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44265</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44203</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44421</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>44085</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44078</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44644</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44263</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44664</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44792</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44698</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44389</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44491</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44532</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44704</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>44397</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44176</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44143</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44114</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44418</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44407</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44644</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44806</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>44143</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44131</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44090</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>44175</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44662</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44183</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44095</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44095</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44160</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44300</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44517</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44143</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>44398</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44383</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45552</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>44789</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45741</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45693</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45034</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45329</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45250</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45250</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45329</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45097</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>45362</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44830</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45513</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45356</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44872</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>44357</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>45113</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45777</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44935</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45429</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44827</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45343</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45223</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45187</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>44797</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>44497</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44937</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45560</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45323</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45476</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44889</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45785</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45350</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45398.68</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45330</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45792</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>45611</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20163,7 +20163,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45535</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>44949</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44558</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45435</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45635</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45798</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45798</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44644</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45797</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45189</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45800</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>45723</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44581</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44964</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>45329</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45072</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44909</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45341</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45632.47288194444</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45800</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>44162</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45148</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45224</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>45405</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45442.51335648148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45611</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45807.565</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45201</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44110</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45810</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45572.62424768518</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>45741</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44882</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45813</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45198</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44910</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44382</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45820</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44697</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45634</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45428</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44714</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45252</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45148</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>44397</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44972</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45238</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>45632.49576388889</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45629.66504629629</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45678</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45189</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45831</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45831</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45832</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44342</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>44648</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>44742</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45832</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45832</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45874</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>45833</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45833</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45751</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45723</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45222</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45453</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>45274</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44242</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>45835</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44228</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45836</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45838</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>44792</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45838</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45761</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45840</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45840</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45607</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34684,7 +34684,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45607</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45839</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45756</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45463</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45671</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45356</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44725</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>45769.63487268519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45001</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45841</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45841</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45306</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45887.38813657407</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45607</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45888.66804398148</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45888.6709375</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45888.34069444444</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45887.63130787037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44755</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>44755</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45226</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45889.45498842592</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45889.39368055556</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>45159</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45889.63824074074</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45890.60149305555</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45670</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38080,7 +38080,7 @@
         <v>45274</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45894.48280092593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45616</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>44792</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45198</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45761</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>45196</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>44973</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45896.51576388889</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45896.54671296296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45706</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45896.51166666667</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45896.55414351852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>45895.64844907408</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45336</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45877</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45895.56866898148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45896.52034722222</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45895.41193287037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45897.42265046296</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>45897.50747685185</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>45761</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>45068</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>45897.65035879629</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>45898.34895833334</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40710,7 +40710,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45898.4618287037</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40943,7 +40943,7 @@
         <v>45897.5841087963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>44397</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
         <v>45267</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45182</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45706</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45028</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>44417</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>44826</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>44117</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>45160</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45677</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45329</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44960</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45419.72936342593</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44802</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45173</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45727</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45281</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45579</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>45180</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45175</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45134</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>45632.47732638889</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>44658</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45428</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45428</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>44834</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>44148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45757</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>44384</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>44987</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>44256</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>44887</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45758</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>45105</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45099</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>44412</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>44804</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>44314</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46416,7 +46416,7 @@
         <v>45678</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45751</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45751</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>44466</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45195</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47514,7 +47514,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45148</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45189</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
         <v>45678</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>44739</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>45548</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48912,7 +48912,7 @@
         <v>45762</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
         <v>45632.50675925926</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45758</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>45331</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49678,7 +49678,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49792,7 +49792,7 @@
         <v>44824</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49849,7 +49849,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49911,7 +49911,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45579</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50139,7 +50139,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50196,7 +50196,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45258</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50310,7 +50310,7 @@
         <v>45203</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45771</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50662,7 +50662,7 @@
         <v>45250</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>45632.4877662037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45632.46594907407</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44664</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44456</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45694</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45841</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45332</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45117</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44110</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>45591</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44817</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45331</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>45827</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>45316</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45327</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>44091</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>45790</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44916</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45818</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44937</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45671</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45820</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45671</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>44943</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44851</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44257</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>45793</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45069</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44965</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>45117</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45827</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>45040</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45898.40256944444</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45201</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45092</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44098</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44096</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44160</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44077</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44459</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>44256</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44256</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44447</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>44470</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44775</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>44648</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44648</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44742</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44755</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44169</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>44860</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44407</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44636</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44698</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44529</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44475</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44874</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>44827</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44571</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44648</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44648</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44648</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44242</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44161</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>44179</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44147</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44183</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44169</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>44365</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44224</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44658</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44091</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44466</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>44466</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>44349</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>44419</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>44648</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44648</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44648</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44265</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44203</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44421</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>44085</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44078</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44644</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44263</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44664</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44792</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44698</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44389</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44491</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44532</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44704</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>44397</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44176</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44143</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44114</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44418</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44407</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44644</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44806</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>44143</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44131</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44090</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>44175</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44662</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44183</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44095</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44095</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44160</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44300</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44517</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44143</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>44398</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44383</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45552</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>44789</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45741</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45693</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45034</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45329</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45250</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45250</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45329</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45097</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>45362</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44830</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45513</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45356</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44872</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>44357</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>45113</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45777</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44935</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45429</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44827</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45343</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45223</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45187</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>44797</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>44497</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44937</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45560</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45323</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45476</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44889</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45785</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45350</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45398.68</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45330</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45792</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>45611</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20163,7 +20163,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45535</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>44949</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44558</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45435</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45635</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45798</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45798</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44644</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45797</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45189</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45800</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>45723</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44581</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44964</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>45329</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45072</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44909</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45341</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45632.47288194444</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45800</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>44162</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45148</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45224</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>45405</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45442.51335648148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45611</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45807.565</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45201</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44110</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45810</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45572.62424768518</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>45741</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44882</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45813</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45198</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44910</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44382</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45820</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44697</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45634</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45428</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44714</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45252</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45148</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>44397</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44972</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45238</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>45632.49576388889</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45629.66504629629</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45678</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45189</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45831</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45831</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45832</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44342</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>44648</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>44742</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45832</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45832</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45874</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>45833</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45833</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45751</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45723</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45222</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45453</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>45274</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44242</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>45835</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44228</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45836</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45838</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>44792</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45838</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45761</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45840</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45840</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45607</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34684,7 +34684,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45607</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45839</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45756</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45463</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45671</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45356</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44725</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>45769.63487268519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45001</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45841</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45841</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45306</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45887.38813657407</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45607</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45888.66804398148</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45888.6709375</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45888.34069444444</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45887.63130787037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44755</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>44755</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45226</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45889.45498842592</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45889.39368055556</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>45159</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45889.63824074074</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45890.60149305555</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45670</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38080,7 +38080,7 @@
         <v>45274</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45894.48280092593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45616</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>44792</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45198</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45761</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>45196</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>44973</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45896.51576388889</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45896.54671296296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45706</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45896.51166666667</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45896.55414351852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>45895.64844907408</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45336</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45877</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45895.56866898148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45896.52034722222</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45895.41193287037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45897.42265046296</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>45897.50747685185</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>45761</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>45068</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>45897.65035879629</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>45898.34895833334</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40710,7 +40710,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45898.4618287037</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40943,7 +40943,7 @@
         <v>45897.5841087963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>44397</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
         <v>45267</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45182</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45706</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45028</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>44417</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>44826</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>44117</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>45160</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45677</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45329</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44960</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45419.72936342593</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44802</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45173</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45727</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45281</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45579</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>45180</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45175</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45134</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>45632.47732638889</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>44658</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45428</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45428</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>44834</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>44148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45757</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>44384</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>44987</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>44256</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>44887</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45758</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>45105</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45099</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>44412</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>44804</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>44314</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46416,7 +46416,7 @@
         <v>45678</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45751</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45751</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>44466</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45195</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47514,7 +47514,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45148</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45189</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
         <v>45678</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>44739</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>45548</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48912,7 +48912,7 @@
         <v>45762</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
         <v>45632.50675925926</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45758</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>45331</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49678,7 +49678,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49792,7 +49792,7 @@
         <v>44824</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49849,7 +49849,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49911,7 +49911,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45579</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50139,7 +50139,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50196,7 +50196,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45258</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50310,7 +50310,7 @@
         <v>45203</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45771</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50662,7 +50662,7 @@
         <v>45250</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>45632.4877662037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45632.46594907407</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44456</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>44664</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45694</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45841</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45332</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44110</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>45591</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>44817</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>45331</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45901.476875</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45827</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45327</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>45316</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44937</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45790</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>44943</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44916</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45818</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45820</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45671</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>45671</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44257</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45793</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>45201</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45069</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>45117</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45827</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45040</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>45898.40256944444</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44965</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45092</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44096</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44530</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44160</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44256</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44459</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44256</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44447</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44470</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44775</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44648</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44648</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44742</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44755</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44860</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44169</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44407</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44636</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>44698</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>44529</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44475</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44874</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>44827</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>44571</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44648</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44648</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44648</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44242</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44161</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44179</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44147</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>44183</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44169</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44407</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44365</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44224</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44658</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44091</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44466</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44466</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44349</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44419</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44648</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44648</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>44648</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44265</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>44203</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>44421</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>44263</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44664</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44698</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44389</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44491</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>44792</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44532</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>44704</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44397</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44114</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44176</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44407</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44644</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44143</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44418</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44806</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>44143</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44175</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44131</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44183</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44160</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44090</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44662</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44095</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44095</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44300</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44517</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>44085</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>44398</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44412</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44143</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44826</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44644</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45634</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44792</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44792</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>45040</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45761</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45769.63487268519</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45727</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>44935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>45175</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45072</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45777</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>45187</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45343</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45632.49576388889</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45182</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45476</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45785</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44910</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44755</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45350</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>45330</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45678</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>45611</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45329</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45341</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45252</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45548</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44497</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>45198</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44383</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45579</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45362</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45535</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45099</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>44834</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44960</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45148</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44228</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45792</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45356</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44945</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45771</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45678</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45034</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45201</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45267</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45635</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45797</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45741</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>44658</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45001</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45435</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45428</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45428</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>44909</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45798</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45798</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>44972</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>44397</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45203</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45723</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>45258</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45226</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>45274</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45800</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>45159</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>44887</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45222</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44148</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>44110</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>44581</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45611</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45306</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45148</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45800</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45807.565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45463</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>44384</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>45572.62424768518</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44872</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45632.47288194444</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45810</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44882</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44937</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45813</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>45232</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>45238</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>45756</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44256</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>45819</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45616</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>45820</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>45579</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>45831</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>45831</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45677</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>44789</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45832</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>45671</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32472,7 +32472,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>44342</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45833</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45097</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45832</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45160</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45832</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>45833</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>44242</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45835</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>44382</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45250</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45250</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>44987</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45838</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45838</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45836</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45840</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45841</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>45068</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45189</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45840</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34740,7 +34740,7 @@
         <v>45841</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>45887.38813657407</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45845</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45105</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45887.63130787037</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45113</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45889.45498842592</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45888</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45889.39368055556</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45889.63824074074</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45888.66804398148</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45888.6709375</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45888.34069444444</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45148</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45890.60149305555</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45895.64844907408</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45894.48280092593</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45895.56866898148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45895.41193287037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45896.51166666667</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45896.52034722222</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>45897.42265046296</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45897.65035879629</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45896.54671296296</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45877</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45897.5841087963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45896.51576388889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45896.55414351852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45897.50747685185</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45898.4618287037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45899.40962962963</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45900.66130787037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45898.34895833334</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45899.39414351852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45901.48072916667</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45900.63513888889</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>45903.49555555556</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45902.35120370371</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45903.48692129629</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45429</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>44697</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>45428</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44964</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45903</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45904.59798611111</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45905.33054398148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45198</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>45629.66504629629</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>45905.32061342592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45329</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45607</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45223</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45398.68</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44714</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45054</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45356</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45281</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>45751</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45632.50675925926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>45607</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>45560</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>44830</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45331</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>44792</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44973</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45607</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44873</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>45670</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45195</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45224</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>45329</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45329</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45632.46594907407</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43381,7 +43381,7 @@
         <v>44802</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43500,7 +43500,7 @@
         <v>45405</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>44117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>45723</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45751</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>44725</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>44162</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45758</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>45693</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>45323</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>45632.4877662037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>44827</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45678</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>44417</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45148</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45552</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45762</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>44644</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45761</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45761</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>45274</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>44797</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>44397</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45758</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46440,7 +46440,7 @@
         <v>44824</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46554,7 +46554,7 @@
         <v>45189</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>45189</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>44742</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45741</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>44739</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45336</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>44949</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45189</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>45632.47732638889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47486,7 +47486,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47543,7 +47543,7 @@
         <v>45706</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45028</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45757</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45134</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45250</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>44558</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>44466</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45180</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45173</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44314</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>44889</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>44357</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45188</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>44804</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50168,7 +50168,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50282,7 +50282,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50344,7 +50344,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>44755</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45453</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45196</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45751</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>44648</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45513</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44664</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44456</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45694</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45841</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45332</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45117</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44110</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>45591</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44817</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45331</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45901.476875</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45827</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45316</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45327</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44916</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>45818</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>44937</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45671</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>45671</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>45820</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44943</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44257</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45793</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>45069</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45117</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44965</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>45827</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45040</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>45898.40256944444</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45201</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45092</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44096</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44530</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44160</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44256</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>44256</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44459</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44447</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44470</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44648</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44648</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44775</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44742</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44755</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44169</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44860</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44407</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44698</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>44874</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>44529</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44475</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>44827</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>44571</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44648</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44648</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44648</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44242</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44161</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44183</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44566</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44368</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44169</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44179</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44147</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44407</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44365</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44224</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44658</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44091</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44466</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44466</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44349</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44648</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44648</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44648</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>44265</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44203</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>44419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>44421</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44644</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44664</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44698</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44263</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44792</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44389</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44491</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44704</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44176</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>44397</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44532</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44806</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44114</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>44407</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>44644</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44090</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44160</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44175</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44183</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44662</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44095</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44095</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44143</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44418</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44383</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44143</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45552</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44789</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45097</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>45362</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45329</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>44830</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45741</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>45693</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>45356</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44872</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45034</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44357</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45329</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45250</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>45250</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44143</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45513</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44935</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45429</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44827</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45113</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45223</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44131</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45777</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45343</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44797</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45187</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44497</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45560</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>44937</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45398.68</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45323</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44889</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45476</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45785</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45350</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45330</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45611</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45792</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>44300</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44517</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45535</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44949</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>44558</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>44398</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44644</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44581</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45072</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45435</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45635</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45341</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45798</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45798</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45797</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45189</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45148</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45800</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45723</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45224</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>44964</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45329</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45611</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>44909</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45201</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>44110</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>45800</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44162</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>45232</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45405</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45807.565</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45810</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44697</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>44882</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45148</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45198</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45813</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45238</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>44910</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>44382</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44342</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45819</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>44742</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45820</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45634</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45751</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45428</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44714</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45252</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45723</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45222</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>44397</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>44972</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44228</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44792</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45678</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>45831</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45831</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45761</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45832</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45189</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>45832</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45832</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45756</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45874</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44648</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45833</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>45833</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45463</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45671</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>44945</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45356</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44725</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45453</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45274</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>44242</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45835</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>45836</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45838</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>45306</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45838</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45840</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45607</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45607</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45001</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44755</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>44755</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45226</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35350,7 +35350,7 @@
         <v>45840</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45607</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45274</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45159</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45670</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45616</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>44792</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45198</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44973</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45706</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>45761</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45068</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45196</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>44397</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45336</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45182</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45706</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44826</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45841</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44117</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45160</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45677</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45329</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45841</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>45761</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>45173</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39507,7 +39507,7 @@
         <v>45727</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45175</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45134</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45267</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>44148</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45887.38813657407</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>45757</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44887</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45758</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45105</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41242,7 +41242,7 @@
         <v>45845</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>44417</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45888.66804398148</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45888.6709375</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45888.34069444444</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>44412</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45887.63130787037</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45040</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>44873</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41817,7 +41817,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45889.45498842592</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45889.39368055556</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>44804</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42288,7 +42288,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45889.63824074074</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45890.60149305555</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45888</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45751</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45751</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45894.48280092593</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>44960</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>44802</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45281</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43453,7 +43453,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45896.51576388889</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45896.54671296296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>45579</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45896.51166666667</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45896.55414351852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45895.64844907408</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>45877</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>45895.56866898148</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45896.52034722222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45895.41193287037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45897.42265046296</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45897.50747685185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45180</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45897.65035879629</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45898.34895833334</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45898.4618287037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45897.5841087963</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45899.39414351852</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44846,7 +44846,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45902.35120370371</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>45900.66130787037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45901.48072916667</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>44658</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45900.63513888889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45899.40962962963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45428</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>45428</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45904.59798611111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>45903</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>44834</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>44384</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44987</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45721,7 +45721,7 @@
         <v>45903.48692129629</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>44256</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>45903.49555555556</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45908.62725694444</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45099</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45905.32061342592</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45908.60138888889</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>44314</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45905.33054398148</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46554,7 +46554,7 @@
         <v>45678</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>45910.55814814815</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45910.43978009259</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>45909.56905092593</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>44466</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45910.62370370371</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45910.62987268518</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45910.63303240741</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47253,7 +47253,7 @@
         <v>45909.62510416667</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47372,7 +47372,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45911</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45912.64748842592</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>45911.55575231482</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45911.36196759259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45572</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45911.6139699074</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45911.64164351852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45195</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45188</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45189</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45189</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45678</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>44739</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45548</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>45762</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50168,7 +50168,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50282,7 +50282,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50339,7 +50339,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>45758</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45331</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50634,7 +50634,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50748,7 +50748,7 @@
         <v>44824</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50867,7 +50867,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50924,7 +50924,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50981,7 +50981,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>45579</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51152,7 +51152,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>45258</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45203</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45771</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51618,7 +51618,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51732,7 +51732,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44664</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44456</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45694</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45841</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45332</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45117</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44110</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>45591</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44817</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45331</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45901.476875</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45827</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45316</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45327</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44916</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>45818</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>44937</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45671</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>45671</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>45820</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44943</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44257</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45793</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>45069</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45117</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44965</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>45827</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45040</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>45898.40256944444</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45201</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45092</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44096</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44530</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44160</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44256</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>44256</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44459</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44447</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44470</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44648</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44648</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44775</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44742</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44755</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44169</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44860</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44407</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44698</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>44874</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>44529</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44475</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>44827</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>44571</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44648</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44648</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44648</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44242</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44161</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44183</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44566</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44368</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>44169</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44179</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44147</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44407</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44365</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44224</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44658</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44091</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44466</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44466</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44349</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44648</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44648</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44648</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>44265</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44203</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>44419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>44421</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44644</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44664</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44698</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44263</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44792</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44389</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44491</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44704</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44176</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>44397</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44532</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44806</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44114</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>44407</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>44644</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44090</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44160</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44175</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44183</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44662</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44095</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44095</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44143</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44418</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44383</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44143</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45552</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44789</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45097</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>45362</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45329</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>44830</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45741</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>45693</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>45356</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44872</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45034</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44357</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45329</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45250</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>45250</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44143</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45513</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44935</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45429</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44827</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45113</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45223</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44131</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45777</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45343</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44797</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45187</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44497</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45560</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>44937</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45398.68</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45323</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44889</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45476</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45785</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45350</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45330</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45611</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45792</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>44300</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44517</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45535</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44949</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>44558</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>44398</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44644</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44581</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45072</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45435</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45635</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45341</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45798</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45798</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45797</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45189</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45148</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45800</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45723</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45224</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>44964</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45329</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45611</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>44909</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45201</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>44110</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>45800</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44162</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>45232</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45405</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45807.565</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45442.50618055555</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45810</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44697</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>44882</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45148</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45198</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45813</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45238</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>44910</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>44382</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44342</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45819</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>44742</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45820</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45634</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45751</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45428</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44714</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45252</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45723</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45222</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>44397</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>44972</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45761.44952546297</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44228</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44792</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45678</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>45831</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45831</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45761</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45832</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45189</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>45832</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45832</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45756</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45874</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44648</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45833</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>45833</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45463</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45671</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>44945</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45356</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44725</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45453</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45274</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>44242</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45835</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>45836</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45838</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>45306</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45838</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45840</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45607</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45607</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45001</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44755</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>44755</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45226</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35350,7 +35350,7 @@
         <v>45840</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45607</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45274</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45159</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45670</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45616</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>44792</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45198</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44973</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45706</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>45761</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45068</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45196</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>44397</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45336</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45182</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45706</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45749.46744212963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44826</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45841</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44117</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45160</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45677</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45329</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45841</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>45761</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>45173</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39507,7 +39507,7 @@
         <v>45727</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45175</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45134</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45267</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>44148</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45887.38813657407</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>45757</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44887</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45758</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45105</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41242,7 +41242,7 @@
         <v>45845</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>44417</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45888.66804398148</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45888.6709375</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45888.34069444444</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>44412</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45887.63130787037</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45040</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>44873</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41817,7 +41817,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45889.45498842592</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45889.39368055556</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>44804</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42288,7 +42288,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45889.63824074074</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45890.60149305555</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45888</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45751</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45751</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45894.48280092593</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>44960</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>44802</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45281</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43453,7 +43453,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45896.51576388889</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45896.54671296296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>45579</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45896.51166666667</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45896.55414351852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45895.64844907408</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>45877</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>45895.56866898148</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45896.52034722222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45895.41193287037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45897.42265046296</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45897.50747685185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45180</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45897.65035879629</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45898.34895833334</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45898.4618287037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45897.5841087963</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45899.39414351852</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44846,7 +44846,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45902.35120370371</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>45900.66130787037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45901.48072916667</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>44658</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45900.63513888889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45899.40962962963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45428</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>45428</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45904.59798611111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>45903</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>44834</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>44384</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44987</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45721,7 +45721,7 @@
         <v>45903.48692129629</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>44256</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>45903.49555555556</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45908.62725694444</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45099</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45905.32061342592</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45908.60138888889</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>44314</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45905.33054398148</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46554,7 +46554,7 @@
         <v>45678</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>45910.55814814815</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45910.43978009259</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>45909.56905092593</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>44466</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45910.62370370371</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45910.62987268518</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45910.63303240741</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47253,7 +47253,7 @@
         <v>45909.62510416667</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47372,7 +47372,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45911</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45912.64748842592</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>45911.55575231482</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45911.36196759259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45572</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45911.6139699074</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45911.64164351852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45195</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45188</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45189</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45189</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45678</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>44739</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45548</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>45762</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50168,7 +50168,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50282,7 +50282,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50339,7 +50339,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>45758</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45331</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50634,7 +50634,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50748,7 +50748,7 @@
         <v>44824</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50867,7 +50867,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50924,7 +50924,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50981,7 +50981,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>45579</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51152,7 +51152,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>45258</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45203</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45771</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51618,7 +51618,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51732,7 +51732,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45901.476875</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>44456</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>44664</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1290,14 +1290,14 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27017-2025</t>
+          <t>A 33371-2025</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>45811.56905092593</v>
+        <v>45841</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1309,17 +1309,22 @@
           <t>FALUN</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G9" t="n">
-        <v>11.7</v>
+        <v>17.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -1334,15 +1339,115 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Garnlav
+Tretåig hackspett
+Ullticka
+Vedtrappmossa
+Bronshjon
+Dropptaggsvamp
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="S9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2080/artfynd/A 33371-2025 artfynd.xlsx", "A 33371-2025")</f>
+        <v/>
+      </c>
+      <c r="T9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2080/kartor/A 33371-2025 karta.png", "A 33371-2025")</f>
+        <v/>
+      </c>
+      <c r="U9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2080/knärot/A 33371-2025 karta knärot.png", "A 33371-2025")</f>
+        <v/>
+      </c>
+      <c r="V9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2080/klagomål/A 33371-2025 FSC-klagomål.docx", "A 33371-2025")</f>
+        <v/>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2080/klagomålsmail/A 33371-2025 FSC-klagomål mail.docx", "A 33371-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2080/tillsyn/A 33371-2025 tillsynsbegäran.docx", "A 33371-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2080/tillsynsmail/A 33371-2025 tillsynsbegäran mail.docx", "A 33371-2025")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2080/fåglar/A 33371-2025 prioriterade fågelarter.docx", "A 33371-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 27017-2025</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>45811.56905092593</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>45927</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FALUN</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
         <v>7</v>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka
@@ -1353,95 +1458,95 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="S9">
+      <c r="S10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/artfynd/A 27017-2025 artfynd.xlsx", "A 27017-2025")</f>
         <v/>
       </c>
-      <c r="T9">
+      <c r="T10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/kartor/A 27017-2025 karta.png", "A 27017-2025")</f>
         <v/>
       </c>
-      <c r="U9">
+      <c r="U10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/knärot/A 27017-2025 karta knärot.png", "A 27017-2025")</f>
         <v/>
       </c>
-      <c r="V9">
+      <c r="V10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/klagomål/A 27017-2025 FSC-klagomål.docx", "A 27017-2025")</f>
         <v/>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/klagomålsmail/A 27017-2025 FSC-klagomål mail.docx", "A 27017-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/tillsyn/A 27017-2025 tillsynsbegäran.docx", "A 27017-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/tillsynsmail/A 27017-2025 tillsynsbegäran mail.docx", "A 27017-2025")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/fåglar/A 27017-2025 prioriterade fågelarter.docx", "A 27017-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 5812-2025</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B11" s="1" t="n">
         <v>45694</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>45926</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>FALUN</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="C11" s="1" t="n">
+        <v>45927</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FALUN</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>11.7</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" t="n">
         <v>7</v>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka
@@ -1452,143 +1557,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="S10">
+      <c r="S11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/artfynd/A 5812-2025 artfynd.xlsx", "A 5812-2025")</f>
         <v/>
       </c>
-      <c r="T10">
+      <c r="T11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/kartor/A 5812-2025 karta.png", "A 5812-2025")</f>
         <v/>
       </c>
-      <c r="U10">
+      <c r="U11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/knärot/A 5812-2025 karta knärot.png", "A 5812-2025")</f>
         <v/>
       </c>
-      <c r="V10">
+      <c r="V11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/klagomål/A 5812-2025 FSC-klagomål.docx", "A 5812-2025")</f>
         <v/>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/klagomålsmail/A 5812-2025 FSC-klagomål mail.docx", "A 5812-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/tillsyn/A 5812-2025 tillsynsbegäran.docx", "A 5812-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/tillsynsmail/A 5812-2025 tillsynsbegäran mail.docx", "A 5812-2025")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2080/fåglar/A 5812-2025 prioriterade fågelarter.docx", "A 5812-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 33371-2025</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>45841</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>45926</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>FALUN</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Garnlav
-Tretåig hackspett
-Ullticka
-Bronshjon
-Dropptaggsvamp
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="S11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2080/artfynd/A 33371-2025 artfynd.xlsx", "A 33371-2025")</f>
-        <v/>
-      </c>
-      <c r="T11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2080/kartor/A 33371-2025 karta.png", "A 33371-2025")</f>
-        <v/>
-      </c>
-      <c r="U11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2080/knärot/A 33371-2025 karta knärot.png", "A 33371-2025")</f>
-        <v/>
-      </c>
-      <c r="V11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2080/klagomål/A 33371-2025 FSC-klagomål.docx", "A 33371-2025")</f>
-        <v/>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2080/klagomålsmail/A 33371-2025 FSC-klagomål mail.docx", "A 33371-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2080/tillsyn/A 33371-2025 tillsynsbegäran.docx", "A 33371-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2080/tillsynsmail/A 33371-2025 tillsynsbegäran mail.docx", "A 33371-2025")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2080/fåglar/A 33371-2025 prioriterade fågelarter.docx", "A 33371-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1599,7 +1600,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1697,7 +1698,7 @@
         <v>45332</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1793,7 @@
         <v>44110</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,7 +1883,7 @@
         <v>45117</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1985,7 +1986,7 @@
         <v>45591</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,7 +2080,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2176,7 +2177,7 @@
         <v>44817</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2265,7 +2266,7 @@
         <v>45331</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,7 +2355,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2450,7 +2451,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,7 +2543,7 @@
         <v>45327</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2633,7 +2634,7 @@
         <v>45316</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2720,7 +2721,7 @@
         <v>45827</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2811,7 +2812,7 @@
         <v>44937</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2901,7 +2902,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2992,7 +2993,7 @@
         <v>44943</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3078,7 +3079,7 @@
         <v>44916</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3172,7 +3173,7 @@
         <v>45818</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3258,7 +3259,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3344,7 +3345,7 @@
         <v>45671</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3430,7 +3431,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3516,7 +3517,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3606,7 +3607,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3696,7 +3697,7 @@
         <v>45820</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3790,7 +3791,7 @@
         <v>45671</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3880,7 +3881,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3970,7 +3971,7 @@
         <v>44851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4059,7 +4060,7 @@
         <v>44257</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4144,7 +4145,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4233,7 +4234,7 @@
         <v>45793</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4323,7 +4324,7 @@
         <v>45201</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4412,7 +4413,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4497,7 +4498,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4586,7 +4587,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4680,7 +4681,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4770,7 +4771,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4860,7 +4861,7 @@
         <v>45069</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4945,7 +4946,7 @@
         <v>45117</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5039,7 +5040,7 @@
         <v>45040</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5124,7 +5125,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5213,7 +5214,7 @@
         <v>44965</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5302,7 +5303,7 @@
         <v>45827</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5387,7 +5388,7 @@
         <v>45092</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5476,7 +5477,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5565,7 +5566,7 @@
         <v>45898.40256944444</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5654,7 +5655,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5744,7 +5745,7 @@
         <v>45646.84287037037</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5829,7 +5830,7 @@
         <v>45917.64488425926</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5918,7 +5919,7 @@
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5975,7 +5976,7 @@
         <v>44160</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6032,7 +6033,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6089,7 +6090,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6146,7 +6147,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6203,7 +6204,7 @@
         <v>44459</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6260,7 +6261,7 @@
         <v>44256</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6317,7 +6318,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6374,7 +6375,7 @@
         <v>44256</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6431,7 +6432,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6493,7 +6494,7 @@
         <v>44447</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6555,7 +6556,7 @@
         <v>44648</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6612,7 +6613,7 @@
         <v>44648</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6669,7 +6670,7 @@
         <v>44470</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6726,7 +6727,7 @@
         <v>44775</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6783,7 +6784,7 @@
         <v>44742</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6845,7 +6846,7 @@
         <v>44755</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6902,7 +6903,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6959,7 +6960,7 @@
         <v>44169</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7021,7 +7022,7 @@
         <v>44860</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7078,7 +7079,7 @@
         <v>44407</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7135,7 +7136,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7192,7 +7193,7 @@
         <v>44636</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7249,7 +7250,7 @@
         <v>44698</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7311,7 +7312,7 @@
         <v>44529</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7368,7 +7369,7 @@
         <v>44475</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7425,7 +7426,7 @@
         <v>44874</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7482,7 +7483,7 @@
         <v>44827</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7539,7 +7540,7 @@
         <v>44571</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7596,7 +7597,7 @@
         <v>44648</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7653,7 +7654,7 @@
         <v>44648</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7710,7 +7711,7 @@
         <v>44648</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7767,7 +7768,7 @@
         <v>44242</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7824,7 +7825,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7881,7 +7882,7 @@
         <v>44161</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7943,7 +7944,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8000,7 +8001,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8062,7 +8063,7 @@
         <v>44179</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8119,7 +8120,7 @@
         <v>44147</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8176,7 +8177,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8233,7 +8234,7 @@
         <v>44183</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8295,7 +8296,7 @@
         <v>44566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8352,7 +8353,7 @@
         <v>44368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8409,7 +8410,7 @@
         <v>44169</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8491,7 +8492,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8548,7 +8549,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8605,7 +8606,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8662,7 +8663,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8724,7 +8725,7 @@
         <v>44407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8781,7 +8782,7 @@
         <v>44365</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8838,7 +8839,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8895,7 +8896,7 @@
         <v>44224</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8952,7 +8953,7 @@
         <v>44658</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9009,7 +9010,7 @@
         <v>44466</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9066,7 +9067,7 @@
         <v>44466</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9123,7 +9124,7 @@
         <v>44349</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9180,7 +9181,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9237,7 +9238,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9294,7 +9295,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9351,7 +9352,7 @@
         <v>44419</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9408,7 +9409,7 @@
         <v>44265</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9465,7 +9466,7 @@
         <v>44648</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9522,7 +9523,7 @@
         <v>44648</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9579,7 +9580,7 @@
         <v>44648</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9636,7 +9637,7 @@
         <v>44203</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9693,7 +9694,7 @@
         <v>44421</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9750,7 +9751,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9807,7 +9808,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9864,7 +9865,7 @@
         <v>44263</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9921,7 +9922,7 @@
         <v>44389</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9978,7 +9979,7 @@
         <v>44491</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10035,7 +10036,7 @@
         <v>44792</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10092,7 +10093,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10154,7 +10155,7 @@
         <v>44532</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10211,7 +10212,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10268,7 +10269,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10325,7 +10326,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10387,7 +10388,7 @@
         <v>44704</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10449,7 +10450,7 @@
         <v>44397</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10506,7 +10507,7 @@
         <v>44176</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10568,7 +10569,7 @@
         <v>44114</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10625,7 +10626,7 @@
         <v>44143</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10687,7 +10688,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10744,7 +10745,7 @@
         <v>44418</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10801,7 +10802,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10863,7 +10864,7 @@
         <v>44644</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10920,7 +10921,7 @@
         <v>44407</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10977,7 +10978,7 @@
         <v>44644</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11034,7 +11035,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11091,7 +11092,7 @@
         <v>44143</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11148,7 +11149,7 @@
         <v>44664</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11210,7 +11211,7 @@
         <v>44131</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11267,7 +11268,7 @@
         <v>44698</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11329,7 +11330,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11386,7 +11387,7 @@
         <v>44662</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11443,7 +11444,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11505,7 +11506,7 @@
         <v>44175</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11562,7 +11563,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11619,7 +11620,7 @@
         <v>44183</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11681,7 +11682,7 @@
         <v>44143</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11743,7 +11744,7 @@
         <v>44300</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11800,7 +11801,7 @@
         <v>44517</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11857,7 +11858,7 @@
         <v>44398</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11914,7 +11915,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11971,7 +11972,7 @@
         <v>45607.55261574074</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12033,7 +12034,7 @@
         <v>45625.4747337963</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12095,7 +12096,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12152,7 +12153,7 @@
         <v>44755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12209,7 +12210,7 @@
         <v>44935</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12266,7 +12267,7 @@
         <v>45735.45020833334</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12323,7 +12324,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12380,7 +12381,7 @@
         <v>45394.57233796296</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12437,7 +12438,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12499,7 +12500,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12581,7 +12582,7 @@
         <v>45611.55175925926</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12643,7 +12644,7 @@
         <v>45040</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12700,7 +12701,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12757,7 +12758,7 @@
         <v>45071.62336805555</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12814,7 +12815,7 @@
         <v>45329</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12871,7 +12872,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12928,7 +12929,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12985,7 +12986,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13042,7 +13043,7 @@
         <v>45727</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13099,7 +13100,7 @@
         <v>45098.60805555555</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13156,7 +13157,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13213,7 +13214,7 @@
         <v>45637.72605324074</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13270,7 +13271,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13327,7 +13328,7 @@
         <v>44412</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13384,7 +13385,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13441,7 +13442,7 @@
         <v>45777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13503,7 +13504,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13560,7 +13561,7 @@
         <v>45625.7271412037</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13617,7 +13618,7 @@
         <v>44826</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13674,7 +13675,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13731,7 +13732,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13788,7 +13789,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13845,7 +13846,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13902,7 +13903,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13959,7 +13960,7 @@
         <v>45187</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14016,7 +14017,7 @@
         <v>45343</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14073,7 +14074,7 @@
         <v>45756.31309027778</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14130,7 +14131,7 @@
         <v>45756.46278935186</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14187,7 +14188,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14244,7 +14245,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14301,7 +14302,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14363,7 +14364,7 @@
         <v>45182</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14420,7 +14421,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14477,7 +14478,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14534,7 +14535,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14591,7 +14592,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14648,7 +14649,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14705,7 +14706,7 @@
         <v>45761</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14767,7 +14768,7 @@
         <v>45476</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14824,7 +14825,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14881,7 +14882,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14943,7 +14944,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15005,7 +15006,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15062,7 +15063,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15119,7 +15120,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15181,7 +15182,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15238,7 +15239,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15295,7 +15296,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15352,7 +15353,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15409,7 +15410,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15471,7 +15472,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15528,7 +15529,7 @@
         <v>45785</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15590,7 +15591,7 @@
         <v>45398.3778587963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15647,7 +15648,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15704,7 +15705,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15761,7 +15762,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15818,7 +15819,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15875,7 +15876,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15932,7 +15933,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15989,7 +15990,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16046,7 +16047,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16103,7 +16104,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16160,7 +16161,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16217,7 +16218,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16274,7 +16275,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16331,7 +16332,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16388,7 +16389,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16445,7 +16446,7 @@
         <v>45350</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16502,7 +16503,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16564,7 +16565,7 @@
         <v>45182.58681712963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16621,7 +16622,7 @@
         <v>45330</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16678,7 +16679,7 @@
         <v>45678</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16735,7 +16736,7 @@
         <v>45751.66671296296</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16792,7 +16793,7 @@
         <v>45611</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16849,7 +16850,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16906,7 +16907,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16968,7 +16969,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17025,7 +17026,7 @@
         <v>45548</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17082,7 +17083,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17139,7 +17140,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17196,7 +17197,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17253,7 +17254,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17310,7 +17311,7 @@
         <v>44806</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17367,7 +17368,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17424,7 +17425,7 @@
         <v>45198</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17481,7 +17482,7 @@
         <v>44383</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17538,7 +17539,7 @@
         <v>45771.55671296296</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17600,7 +17601,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17657,7 +17658,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17714,7 +17715,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17771,7 +17772,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17833,7 +17834,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17895,7 +17896,7 @@
         <v>45349.52979166667</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17952,7 +17953,7 @@
         <v>44228</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18009,7 +18010,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18071,7 +18072,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18133,7 +18134,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18190,7 +18191,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18252,7 +18253,7 @@
         <v>45356</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18309,7 +18310,7 @@
         <v>45341</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18366,7 +18367,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18423,7 +18424,7 @@
         <v>45252</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18480,7 +18481,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18542,7 +18543,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18604,7 +18605,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18661,7 +18662,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18718,7 +18719,7 @@
         <v>45535</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18775,7 +18776,7 @@
         <v>44497</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18837,7 +18838,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18894,7 +18895,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18951,7 +18952,7 @@
         <v>45771</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19013,7 +19014,7 @@
         <v>45761.61626157408</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19070,7 +19071,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19127,7 +19128,7 @@
         <v>45741.56762731481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19184,7 +19185,7 @@
         <v>45748.62056712963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19241,7 +19242,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19303,7 +19304,7 @@
         <v>45756.46113425926</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19360,7 +19361,7 @@
         <v>44160</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19417,7 +19418,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19474,7 +19475,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19536,7 +19537,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19593,7 +19594,7 @@
         <v>45579</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19650,7 +19651,7 @@
         <v>45678</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19707,7 +19708,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19764,7 +19765,7 @@
         <v>45792</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19826,7 +19827,7 @@
         <v>45362</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19883,7 +19884,7 @@
         <v>45034</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19940,7 +19941,7 @@
         <v>45625.57991898148</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20002,7 +20003,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20059,7 +20060,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20116,7 +20117,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20173,7 +20174,7 @@
         <v>45099</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20230,7 +20231,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20287,7 +20288,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20344,7 +20345,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20401,7 +20402,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20458,7 +20459,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20515,7 +20516,7 @@
         <v>44834</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20572,7 +20573,7 @@
         <v>44960</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20629,7 +20630,7 @@
         <v>45148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20691,7 +20692,7 @@
         <v>45201</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20748,7 +20749,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20805,7 +20806,7 @@
         <v>45084.57733796296</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20862,7 +20863,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20924,7 +20925,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20986,7 +20987,7 @@
         <v>45741</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21043,7 +21044,7 @@
         <v>45537.50268518519</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21105,7 +21106,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21167,7 +21168,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21229,7 +21230,7 @@
         <v>45428</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21291,7 +21292,7 @@
         <v>45428</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21353,7 +21354,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21410,7 +21411,7 @@
         <v>45567.67040509259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21467,7 +21468,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21524,7 +21525,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21581,7 +21582,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21643,7 +21644,7 @@
         <v>44945</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21700,7 +21701,7 @@
         <v>45635</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21757,7 +21758,7 @@
         <v>45797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21819,7 +21820,7 @@
         <v>45226</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21876,7 +21877,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21933,7 +21934,7 @@
         <v>45313.33021990741</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21990,7 +21991,7 @@
         <v>45274</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22047,7 +22048,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22104,7 +22105,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22161,7 +22162,7 @@
         <v>45435</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22218,7 +22219,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22275,7 +22276,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22332,7 +22333,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22389,7 +22390,7 @@
         <v>45267</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22446,7 +22447,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22508,7 +22509,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22565,7 +22566,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22622,7 +22623,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22679,7 +22680,7 @@
         <v>45798</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22736,7 +22737,7 @@
         <v>45798</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22793,7 +22794,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22850,7 +22851,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22907,7 +22908,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22964,7 +22965,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23021,7 +23022,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23083,7 +23084,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23145,7 +23146,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23202,7 +23203,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23264,7 +23265,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23321,7 +23322,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23383,7 +23384,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23440,7 +23441,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23497,7 +23498,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23554,7 +23555,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23611,7 +23612,7 @@
         <v>45723</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23668,7 +23669,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23725,7 +23726,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23787,7 +23788,7 @@
         <v>45800</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23849,7 +23850,7 @@
         <v>44658</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23906,7 +23907,7 @@
         <v>45001</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23983,7 +23984,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24040,7 +24041,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24097,7 +24098,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24154,7 +24155,7 @@
         <v>44384</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24216,7 +24217,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24273,7 +24274,7 @@
         <v>45219.46238425926</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24330,7 +24331,7 @@
         <v>44909</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24387,7 +24388,7 @@
         <v>45634</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24444,7 +24445,7 @@
         <v>45692.50388888889</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24501,7 +24502,7 @@
         <v>44972</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24558,7 +24559,7 @@
         <v>44397</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24615,7 +24616,7 @@
         <v>45203</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24672,7 +24673,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24734,7 +24735,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24791,7 +24792,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24848,7 +24849,7 @@
         <v>45800</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24905,7 +24906,7 @@
         <v>44833.40231481481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24962,7 +24963,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25019,7 +25020,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25076,7 +25077,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25133,7 +25134,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25190,7 +25191,7 @@
         <v>45258</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25247,7 +25248,7 @@
         <v>45807.565</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25304,7 +25305,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25361,7 +25362,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25418,7 +25419,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25475,7 +25476,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25532,7 +25533,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25594,7 +25595,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25656,7 +25657,7 @@
         <v>45159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25713,7 +25714,7 @@
         <v>44882</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25770,7 +25771,7 @@
         <v>44887</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25827,7 +25828,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25884,7 +25885,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25941,7 +25942,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25998,7 +25999,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26055,7 +26056,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26112,7 +26113,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26169,7 +26170,7 @@
         <v>45222</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26226,7 +26227,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26283,7 +26284,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26340,7 +26341,7 @@
         <v>44110</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26397,7 +26398,7 @@
         <v>44581</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26454,7 +26455,7 @@
         <v>45611</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26511,7 +26512,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26568,7 +26569,7 @@
         <v>45810</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26625,7 +26626,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26682,7 +26683,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26739,7 +26740,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26801,7 +26802,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26858,7 +26859,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26915,7 +26916,7 @@
         <v>45306</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26972,7 +26973,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27029,7 +27030,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27086,7 +27087,7 @@
         <v>44937</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27143,7 +27144,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27200,7 +27201,7 @@
         <v>45148</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27257,7 +27258,7 @@
         <v>45813</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27314,7 +27315,7 @@
         <v>45232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27371,7 +27372,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27428,7 +27429,7 @@
         <v>45463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27485,7 +27486,7 @@
         <v>45238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27542,7 +27543,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27604,7 +27605,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27661,7 +27662,7 @@
         <v>45756</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27718,7 +27719,7 @@
         <v>44792</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27775,7 +27776,7 @@
         <v>44792</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27832,7 +27833,7 @@
         <v>44872</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27894,7 +27895,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27951,7 +27952,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28028,7 +28029,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28085,7 +28086,7 @@
         <v>45667.55133101852</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28142,7 +28143,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28199,7 +28200,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28256,7 +28257,7 @@
         <v>45611.51700231482</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28318,7 +28319,7 @@
         <v>45819</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28380,7 +28381,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28437,7 +28438,7 @@
         <v>45616</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28494,7 +28495,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28551,7 +28552,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28608,7 +28609,7 @@
         <v>45175</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28665,7 +28666,7 @@
         <v>45072</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28722,7 +28723,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28779,7 +28780,7 @@
         <v>45541.62721064815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28836,7 +28837,7 @@
         <v>45820</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28893,7 +28894,7 @@
         <v>44802.59116898148</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28950,7 +28951,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29007,7 +29008,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29069,7 +29070,7 @@
         <v>45579</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29126,7 +29127,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29183,7 +29184,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29240,7 +29241,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29297,7 +29298,7 @@
         <v>44256</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29354,7 +29355,7 @@
         <v>45389.33204861111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29411,7 +29412,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29468,7 +29469,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29525,7 +29526,7 @@
         <v>44910</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29582,7 +29583,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29639,7 +29640,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29696,7 +29697,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29758,7 +29759,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29815,7 +29816,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29877,7 +29878,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29939,7 +29940,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29996,7 +29997,7 @@
         <v>44789</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30053,7 +30054,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30110,7 +30111,7 @@
         <v>45666.62012731482</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30167,7 +30168,7 @@
         <v>45639.35046296296</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30224,7 +30225,7 @@
         <v>45160</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30281,7 +30282,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30338,7 +30339,7 @@
         <v>44382</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30395,7 +30396,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30457,7 +30458,7 @@
         <v>45250</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30514,7 +30515,7 @@
         <v>45250</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30571,7 +30572,7 @@
         <v>44987</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30628,7 +30629,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30685,7 +30686,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30742,7 +30743,7 @@
         <v>45105</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30799,7 +30800,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30861,7 +30862,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30918,7 +30919,7 @@
         <v>45113</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30975,7 +30976,7 @@
         <v>45677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31032,7 +31033,7 @@
         <v>45671</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31089,7 +31090,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31146,7 +31147,7 @@
         <v>45607.64084490741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31208,7 +31209,7 @@
         <v>45607.64520833334</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31270,7 +31271,7 @@
         <v>44342</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31327,7 +31328,7 @@
         <v>45706</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31389,7 +31390,7 @@
         <v>45097</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31446,7 +31447,7 @@
         <v>44242</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31503,7 +31504,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31565,7 +31566,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31622,7 +31623,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31679,7 +31680,7 @@
         <v>45068</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31736,7 +31737,7 @@
         <v>45189</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31793,7 +31794,7 @@
         <v>45744.34770833333</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31850,7 +31851,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31907,7 +31908,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31969,7 +31970,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32026,7 +32027,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32083,7 +32084,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32140,7 +32141,7 @@
         <v>45148</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32202,7 +32203,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32259,7 +32260,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32321,7 +32322,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32383,7 +32384,7 @@
         <v>44697</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32440,7 +32441,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32497,7 +32498,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32554,7 +32555,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32611,7 +32612,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32668,7 +32669,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32725,7 +32726,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32782,7 +32783,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32839,7 +32840,7 @@
         <v>45429</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32901,7 +32902,7 @@
         <v>45428</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32963,7 +32964,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33020,7 +33021,7 @@
         <v>44629.5853125</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33077,7 +33078,7 @@
         <v>45825.59111111111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33134,7 +33135,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33196,7 +33197,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33253,7 +33254,7 @@
         <v>45460.55043981481</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33310,7 +33311,7 @@
         <v>44964</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33367,7 +33368,7 @@
         <v>45329</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33424,7 +33425,7 @@
         <v>45198</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33481,7 +33482,7 @@
         <v>45825.66074074074</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33563,7 +33564,7 @@
         <v>45607</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33625,7 +33626,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33682,7 +33683,7 @@
         <v>45223</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33739,7 +33740,7 @@
         <v>45398.68</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33796,7 +33797,7 @@
         <v>45427.65140046296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33858,7 +33859,7 @@
         <v>44714</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33920,7 +33921,7 @@
         <v>45054</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33977,7 +33978,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34034,7 +34035,7 @@
         <v>45205.51188657407</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34091,7 +34092,7 @@
         <v>45356</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34148,7 +34149,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34205,7 +34206,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34267,7 +34268,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34324,7 +34325,7 @@
         <v>45281</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34381,7 +34382,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34438,7 +34439,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34495,7 +34496,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34552,7 +34553,7 @@
         <v>45751</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34614,7 +34615,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34671,7 +34672,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34728,7 +34729,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34785,7 +34786,7 @@
         <v>45607</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34847,7 +34848,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34904,7 +34905,7 @@
         <v>44337.53789351852</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34961,7 +34962,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35023,7 +35024,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35080,7 +35081,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35137,7 +35138,7 @@
         <v>44830</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35194,7 +35195,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35251,7 +35252,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35308,7 +35309,7 @@
         <v>45716.29737268519</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35365,7 +35366,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35427,7 +35428,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35489,7 +35490,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35546,7 +35547,7 @@
         <v>45827.30365740741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35603,7 +35604,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35665,7 +35666,7 @@
         <v>45744.3031712963</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35722,7 +35723,7 @@
         <v>45560</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35784,7 +35785,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35846,7 +35847,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35908,7 +35909,7 @@
         <v>45331</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35965,7 +35966,7 @@
         <v>44792</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36022,7 +36023,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36079,7 +36080,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36141,7 +36142,7 @@
         <v>45203.61751157408</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36198,7 +36199,7 @@
         <v>44973</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36255,7 +36256,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36312,7 +36313,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36369,7 +36370,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36431,7 +36432,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36488,7 +36489,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36545,7 +36546,7 @@
         <v>45831.43954861111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36602,7 +36603,7 @@
         <v>45831.37113425926</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36664,7 +36665,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36721,7 +36722,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36778,7 +36779,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36835,7 +36836,7 @@
         <v>45831.6609375</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36892,7 +36893,7 @@
         <v>45831</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36949,7 +36950,7 @@
         <v>45831</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37006,7 +37007,7 @@
         <v>44873</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37063,7 +37064,7 @@
         <v>45831.66144675926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37120,7 +37121,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37182,7 +37183,7 @@
         <v>45607</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37244,7 +37245,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37301,7 +37302,7 @@
         <v>45195</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37358,7 +37359,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37415,7 +37416,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37477,7 +37478,7 @@
         <v>45670</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37534,7 +37535,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37591,7 +37592,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37648,7 +37649,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37705,7 +37706,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37767,7 +37768,7 @@
         <v>45224</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37824,7 +37825,7 @@
         <v>45329</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37881,7 +37882,7 @@
         <v>45832</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37943,7 +37944,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38000,7 +38001,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38062,7 +38063,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38119,7 +38120,7 @@
         <v>45833</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38181,7 +38182,7 @@
         <v>45329</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38238,7 +38239,7 @@
         <v>45832</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38295,7 +38296,7 @@
         <v>44802</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38352,7 +38353,7 @@
         <v>45832</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38414,7 +38415,7 @@
         <v>45603.53417824074</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38476,7 +38477,7 @@
         <v>45833</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38538,7 +38539,7 @@
         <v>45405</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38595,7 +38596,7 @@
         <v>44117</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38657,7 +38658,7 @@
         <v>45835</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38714,7 +38715,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38771,7 +38772,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38828,7 +38829,7 @@
         <v>45834.59554398148</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38885,7 +38886,7 @@
         <v>45835.58814814815</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38942,7 +38943,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38999,7 +39000,7 @@
         <v>45838.65545138889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39056,7 +39057,7 @@
         <v>44725</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39118,7 +39119,7 @@
         <v>44162</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39180,7 +39181,7 @@
         <v>45723</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39237,7 +39238,7 @@
         <v>45758</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39299,7 +39300,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39356,7 +39357,7 @@
         <v>45751</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39418,7 +39419,7 @@
         <v>45838</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39475,7 +39476,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39537,7 +39538,7 @@
         <v>45838</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39594,7 +39595,7 @@
         <v>45836</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39651,7 +39652,7 @@
         <v>45839</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39708,7 +39709,7 @@
         <v>45838.40711805555</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39765,7 +39766,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39822,7 +39823,7 @@
         <v>45840</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39879,7 +39880,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39936,7 +39937,7 @@
         <v>45841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39998,7 +39999,7 @@
         <v>45693</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40075,7 +40076,7 @@
         <v>45840</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40137,7 +40138,7 @@
         <v>45841</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40199,7 +40200,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40256,7 +40257,7 @@
         <v>45887.38813657407</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40318,7 +40319,7 @@
         <v>45323</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40375,7 +40376,7 @@
         <v>44827</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40432,7 +40433,7 @@
         <v>45845</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40489,7 +40490,7 @@
         <v>44417</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40546,7 +40547,7 @@
         <v>45799.41928240741</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40603,7 +40604,7 @@
         <v>45552</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40660,7 +40661,7 @@
         <v>45740.61185185185</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40717,7 +40718,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40774,7 +40775,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40836,7 +40837,7 @@
         <v>45748.67491898148</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40893,7 +40894,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40950,7 +40951,7 @@
         <v>45625.61111111111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41012,7 +41013,7 @@
         <v>45678</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41069,7 +41070,7 @@
         <v>45887.63130787037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41126,7 +41127,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41183,7 +41184,7 @@
         <v>45889.45498842592</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41240,7 +41241,7 @@
         <v>45274</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41297,7 +41298,7 @@
         <v>45888</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41359,7 +41360,7 @@
         <v>45889.39368055556</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41416,7 +41417,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41473,7 +41474,7 @@
         <v>45889.63824074074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41530,7 +41531,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41587,7 +41588,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41644,7 +41645,7 @@
         <v>45148</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41701,7 +41702,7 @@
         <v>45888.66804398148</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41758,7 +41759,7 @@
         <v>45888.6709375</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41815,7 +41816,7 @@
         <v>45888.34069444444</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41877,7 +41878,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41939,7 +41940,7 @@
         <v>45762</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42001,7 +42002,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42058,7 +42059,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42115,7 +42116,7 @@
         <v>44644</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42172,7 +42173,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42229,7 +42230,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42286,7 +42287,7 @@
         <v>45849.58335648148</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42348,7 +42349,7 @@
         <v>45890.60149305555</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42410,7 +42411,7 @@
         <v>45231.47888888889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42467,7 +42468,7 @@
         <v>45849.49446759259</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42524,7 +42525,7 @@
         <v>45761</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42586,7 +42587,7 @@
         <v>45761</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42648,7 +42649,7 @@
         <v>45895.64844907408</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42705,7 +42706,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42762,7 +42763,7 @@
         <v>45894.48280092593</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42819,7 +42820,7 @@
         <v>45895.56866898148</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42876,7 +42877,7 @@
         <v>45624.63219907408</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42933,7 +42934,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42990,7 +42991,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43047,7 +43048,7 @@
         <v>45895.41193287037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43104,7 +43105,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43161,7 +43162,7 @@
         <v>45896.51166666667</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43218,7 +43219,7 @@
         <v>45896.52034722222</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43275,7 +43276,7 @@
         <v>44742</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43337,7 +43338,7 @@
         <v>45897.42265046296</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43399,7 +43400,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43456,7 +43457,7 @@
         <v>45897.65035879629</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43513,7 +43514,7 @@
         <v>45896.54671296296</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43570,7 +43571,7 @@
         <v>45741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43627,7 +43628,7 @@
         <v>45897.5841087963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43684,7 +43685,7 @@
         <v>44739</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43741,7 +43742,7 @@
         <v>45896.51576388889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43798,7 +43799,7 @@
         <v>44797</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43855,7 +43856,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43912,7 +43913,7 @@
         <v>45896.55414351852</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43969,7 +43970,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44031,7 +44032,7 @@
         <v>45897.50747685185</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44088,7 +44089,7 @@
         <v>44397</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44145,7 +44146,7 @@
         <v>45758</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44207,7 +44208,7 @@
         <v>45898.4618287037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44264,7 +44265,7 @@
         <v>44824</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44321,7 +44322,7 @@
         <v>45899.40962962963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44378,7 +44379,7 @@
         <v>45900.66130787037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44435,7 +44436,7 @@
         <v>45898.34895833334</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44497,7 +44498,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44554,7 +44555,7 @@
         <v>45899.39414351852</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44611,7 +44612,7 @@
         <v>45901.48072916667</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44668,7 +44669,7 @@
         <v>45900.63513888889</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44725,7 +44726,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44782,7 +44783,7 @@
         <v>45028</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44839,7 +44840,7 @@
         <v>45903.49555555556</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44901,7 +44902,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44958,7 +44959,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45015,7 +45016,7 @@
         <v>45902.35120370371</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45072,7 +45073,7 @@
         <v>45183.51255787037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45134,7 +45135,7 @@
         <v>45757</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45196,7 +45197,7 @@
         <v>45903.48692129629</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45253,7 +45254,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45310,7 +45311,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45372,7 +45373,7 @@
         <v>45250</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45429,7 +45430,7 @@
         <v>45189</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45486,7 +45487,7 @@
         <v>45189</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45543,7 +45544,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45600,7 +45601,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45657,7 +45658,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45714,7 +45715,7 @@
         <v>44558</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45771,7 +45772,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45828,7 +45829,7 @@
         <v>44466</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45885,7 +45886,7 @@
         <v>45903</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45942,7 +45943,7 @@
         <v>45904.59798611111</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45999,7 +46000,7 @@
         <v>45905.33054398148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46056,7 +46057,7 @@
         <v>45336</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46113,7 +46114,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46170,7 +46171,7 @@
         <v>44949</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46227,7 +46228,7 @@
         <v>45905.32061342592</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46289,7 +46290,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46346,7 +46347,7 @@
         <v>45189</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46403,7 +46404,7 @@
         <v>45909.62510416667</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46465,7 +46466,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46522,7 +46523,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46579,7 +46580,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46641,7 +46642,7 @@
         <v>45180</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46698,7 +46699,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46755,7 +46756,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46817,7 +46818,7 @@
         <v>45173</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46874,7 +46875,7 @@
         <v>45908.62725694444</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46931,7 +46932,7 @@
         <v>45909.56905092593</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46988,7 +46989,7 @@
         <v>45908.60138888889</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47045,7 +47046,7 @@
         <v>45484.42530092593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47102,7 +47103,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47164,7 +47165,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47226,7 +47227,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47288,7 +47289,7 @@
         <v>44314</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47350,7 +47351,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47407,7 +47408,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47464,7 +47465,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47521,7 +47522,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47578,7 +47579,7 @@
         <v>45910.43978009259</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47635,7 +47636,7 @@
         <v>45706</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47697,7 +47698,7 @@
         <v>45911.6139699074</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47759,7 +47760,7 @@
         <v>45911</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47816,7 +47817,7 @@
         <v>45910.62987268518</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47873,7 +47874,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47930,7 +47931,7 @@
         <v>45910.63303240741</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47987,7 +47988,7 @@
         <v>45910.55814814815</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48049,7 +48050,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48111,7 +48112,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48168,7 +48169,7 @@
         <v>45134</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48225,7 +48226,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48282,7 +48283,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48339,7 +48340,7 @@
         <v>44889</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48396,7 +48397,7 @@
         <v>45911.36196759259</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48453,7 +48454,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48510,7 +48511,7 @@
         <v>45911.55575231482</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48572,7 +48573,7 @@
         <v>45911.64164351852</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48634,7 +48635,7 @@
         <v>45910.62370370371</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48691,7 +48692,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48748,7 +48749,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48810,7 +48811,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48867,7 +48868,7 @@
         <v>45302.3704050926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48924,7 +48925,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48981,7 +48982,7 @@
         <v>44804</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49043,7 +49044,7 @@
         <v>45914.86606481481</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49100,7 +49101,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49157,7 +49158,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49219,7 +49220,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49276,7 +49277,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49338,7 +49339,7 @@
         <v>45912.64748842592</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49395,7 +49396,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49457,7 +49458,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49514,7 +49515,7 @@
         <v>45915.54880787037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49571,7 +49572,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49628,7 +49629,7 @@
         <v>45915.57710648148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49685,7 +49686,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49742,7 +49743,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49804,7 +49805,7 @@
         <v>44755</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49861,7 +49862,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49918,7 +49919,7 @@
         <v>45874</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49975,7 +49976,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50032,7 +50033,7 @@
         <v>45453</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50094,7 +50095,7 @@
         <v>45196</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50151,7 +50152,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50208,7 +50209,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50265,7 +50266,7 @@
         <v>45917.48241898148</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50322,7 +50323,7 @@
         <v>44357</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50379,7 +50380,7 @@
         <v>45188</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50436,7 +50437,7 @@
         <v>45916.7175462963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50493,7 +50494,7 @@
         <v>45534.461875</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50555,7 +50556,7 @@
         <v>45918.7181712963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50612,7 +50613,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50669,7 +50670,7 @@
         <v>45607.62606481482</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50731,7 +50732,7 @@
         <v>45918.49219907408</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50788,7 +50789,7 @@
         <v>45670.58552083333</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50845,7 +50846,7 @@
         <v>45877</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50902,7 +50903,7 @@
         <v>45751</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50964,7 +50965,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51021,7 +51022,7 @@
         <v>45741.57155092592</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51083,7 +51084,7 @@
         <v>45735.66260416667</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51140,7 +51141,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51197,7 +51198,7 @@
         <v>44648</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51254,7 +51255,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51311,7 +51312,7 @@
         <v>45513</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51368,7 +51369,7 @@
         <v>45918.71972222222</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51425,7 +51426,7 @@
         <v>45918.70072916667</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51482,7 +51483,7 @@
         <v>45918.70737268519</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51539,7 +51540,7 @@
         <v>45918.45920138889</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51601,7 +51602,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51663,7 +51664,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51720,7 +51721,7 @@
         <v>45628.4153125</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51777,7 +51778,7 @@
         <v>45922.66900462963</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51834,7 +51835,7 @@
         <v>45922.66877314815</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51896,7 +51897,7 @@
         <v>45922.63305555555</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51958,7 +51959,7 @@
         <v>45572</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52015,7 +52016,7 @@
         <v>45923.38413194445</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52072,7 +52073,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52134,7 +52135,7 @@
         <v>45925.54976851852</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52191,7 +52192,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52248,7 +52249,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52305,7 +52306,7 @@
         <v>45925.49892361111</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52362,7 +52363,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>

--- a/Översikt FALUN.xlsx
+++ b/Översikt FALUN.xlsx
@@ -567,7 +567,7 @@
         <v>45202</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>45516</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>45183</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44816</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45901.476875</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>44664</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44456</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45811.56905092593</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45694</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>44466.70864583334</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>45591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>44110</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45332</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>45117</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44817</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>45819.31755787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45331</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>45398.53618055556</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>45827</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45316</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>45327</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>45621.4734375</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44937</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>45820</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44916</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45671</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45727.70813657407</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44943</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45671</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45092.6859375</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>45818</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>45714.52729166667</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45595.5858912037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45043.64988425926</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44257</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>44879.44449074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45898.40256944444</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>45525.64815972222</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45624.48862268519</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45069</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>45646.84287037037</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>45917.64488425926</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44965</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45434.62578703704</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45208.66957175926</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45201</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45092</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45793</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45810.48893518518</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45810.57653935185</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>45807.56452546296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45827</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45603.3166550926</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>45117</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45040</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>44160</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44510.63263888889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44631.53884259259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44536.6465625</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>44459</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44256</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>44587.60530092593</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44256</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>44664.65409722222</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>44447</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44648</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44648</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44470</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44775</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44742</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44755</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44826.67771990741</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44169</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44860</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44407</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44847.64135416667</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44636</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44698</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44529</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>44475</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44874</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44827</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44571</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>44648</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44648</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44648</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>44242</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44161</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44466.70392361111</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44238.72047453704</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44812.6006712963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44179</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44529.46832175926</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44147</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44183</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>44368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>44169</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44879.61891203704</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>44588.86219907407</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44588.66842592593</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>44365</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44693.49159722222</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>44830.58152777778</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44224</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44658</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44466</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44466</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>44349</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>44517.57755787037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>44552.71319444444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>44357.70540509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44419</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44648</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44648</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>44648</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44265</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>44203</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>44421</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44442.53858796296</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44529.5405787037</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44263</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44491</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44389</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44382.90510416667</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>44143</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44418</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>44704</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>44806</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44397</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>44176</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>44114</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>44580.59916666667</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>44143</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>44809.24195601852</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>44131</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>44407</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>44644</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44160</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44328.47465277778</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>44587.86618055555</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44889.89063657408</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44175</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44662</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>44300</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44721.63247685185</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44873.44424768518</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44530.60075231481</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44517</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44398</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44383</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45709.43188657407</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44183</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44819.57239583333</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45513.58015046296</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45329</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>45712.41024305556</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>44143</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>45405.61724537037</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44644</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44531.46664351852</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44664</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44256.6528587963</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>44698</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45054.44313657407</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45567.67582175926</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44831.49181712963</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44789</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45389.32982638889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45356.516875</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45734.32288194444</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45741.57574074074</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45097</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45362</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>45363.28989583333</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44830</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>45356</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45702.63570601852</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44872</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45678.53607638889</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44728.46966435185</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44792</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44532</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44357</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44413.44799768519</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45433.61042824074</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44369.60609953704</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>44935</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45429</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45336</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45852.50997685185</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44827</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45756.45913194444</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45223.63353009259</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>45398.3720949074</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45223</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45445.8946412037</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45634</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45741.41736111111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45428</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44714</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45252</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45252.45018518518</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>45625.46163194445</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45896.51576388889</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>45896.54671296296</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45854.49920138889</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45470.47375</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45896.51166666667</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44901.56976851852</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45896.55414351852</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45895.64844907408</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44322.54041666666</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44397</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45523.7019212963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45523.71026620371</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45523.72092592593</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>44972</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45895.56866898148</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45896.52034722222</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45895.41193287037</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45600.58862268519</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44797</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45897.42265046296</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>45897.50747685185</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45588.56266203704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45588.57958333333</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45566.50581018518</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44796.64291666666</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45232.57947916666</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45637.71758101852</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>44497</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45897.65035879629</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>45898.34895833334</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45898.4618287037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>45440.66130787037</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45307.47775462963</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45897.5841087963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45678</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45899.39414351852</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45267</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45757.39393518519</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45902.35120370371</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>44655.4495949074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45618.68392361111</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>44847.63186342592</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45685.66542824074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>44833.50582175926</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>44937.36425925926</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>44937</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17452,7 +17452,7 @@
         <v>45520.38844907407</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44819.62913194444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45859.44710648148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45900.66130787037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45901.48072916667</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45900.63513888889</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44558.6503125</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>44991.01483796296</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44859.48425925926</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45899.40962962963</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45189</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45323</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45904.59798611111</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45646.41444444445</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44417</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45233.6091087963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45156.4499074074</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44957.47851851852</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45903</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45742.66762731481</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44889</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45072.59862268518</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45533.66743055556</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45903.48692129629</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45755.36767361111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45861.31113425926</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>45523.54817129629</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45903.49555555556</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>44648</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45908.62725694444</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45767.46240740741</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>44945</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45600.4233912037</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45182.66503472222</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45905.32061342592</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45562.6520949074</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45908.60138888889</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45602.36873842592</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45356.50802083333</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>44960</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45624.4871412037</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44802</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45905.33054398148</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45867.43554398148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45559.50664351852</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45020.56026620371</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>45910.55814814815</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45910.43978009259</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45541.62380787037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45453</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45909.56905092593</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>45867.43987268519</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45868.68791666667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45281</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45910.62370370371</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45910.62987268518</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45910.63303240741</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45909.62510416667</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45605.73349537037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45579</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45867.62105324074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45911</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45912.64748842592</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44949</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45446.96997685185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45596.61127314815</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45596.64103009259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45180</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45911.55575231482</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44242</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45911.36196759259</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45607.509375</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45869.40634259259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45911.6139699074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45531.43714120371</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45911.64164351852</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>44327.53788194444</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45373.34085648148</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45373.36180555556</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45365.54184027778</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>44343.84296296296</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45189</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45624.48984953704</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45619.49099537037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>44798.58018518519</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45869.45042824074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45006.63826388889</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45632.40962962963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45607.60332175926</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45365.44188657407</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44298.60944444445</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>44658</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44964</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45574.44925925926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45329</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45545.42612268519</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45428</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45428</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45914.86606481481</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44834</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44909</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>44384</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44987</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45436.44923611111</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44256</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45607</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45611.39648148148</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>45874</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44637.3625925926</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45611.47604166667</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45915.57710648148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45607</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45916.7175462963</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45915.54880787037</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45099</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45581.6672337963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45607.60989583333</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>45590.4653125</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45006.54171296296</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>45611.47130787037</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45918.49219907408</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45624.63408564815</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45001</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45596.61451388889</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45033.61854166666</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45918.45920138889</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45643.63488425926</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45639.38805555556</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44162</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45678</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>44382.91297453704</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45918.7181712963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45918.70072916667</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45918.70737268519</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45918.71972222222</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45565.42178240741</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>44586.57684027778</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45457.46788194445</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45922.66877314815</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45877</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44466</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45922.66900462963</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45607</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45666.61783564815</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45118.65828703704</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44889.3337962963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>45448.48077546297</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45877.56728009259</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45405</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45922.63305555555</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45610.31482638889</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45597.80002314815</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>44865.60775462963</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45659.58495370371</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>44715.45881944444</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>45678.53384259259</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45159</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>44964.5124074074</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45572</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45600.56348379629</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45670</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45670.74568287037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44960.70480324074</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45442.5603125</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45131.55674768519</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45131.56550925926</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45131.57393518519</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45596.60530092593</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45639.59391203704</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45923.38413194445</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45617.81964120371</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45195</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45881.85384259259</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>45741</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45276.37109953703</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45881.84025462963</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45881.86136574074</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45623.585625</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>44882</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45674.64569444444</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45350.40842592593</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45084.52873842593</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45616</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>44887.56288194445</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45523.38677083333</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45561.56046296296</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>45673.97141203703</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45148</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45099.59907407407</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45519.49454861111</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44500.39388888889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45198</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45188</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45567.94900462963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45614.89589120371</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45553.53113425926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44973</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45687.34354166667</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45617.61184027778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>45604.68635416667</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45744.31552083333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>45567.93851851852</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45706</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45758.65826388889</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45454.49690972222</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44910</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45569.65116898148</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45611.36885416666</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>45665.43957175926</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>45554.67652777778</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45068</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>45349.5361574074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45113.64037037037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45189</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45189</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>45678</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45200.8262962963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45771.68155092592</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45625.60799768518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45278.47667824074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45148</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45014.34444444445</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>45741.61945601852</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>44397</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>44739</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>45548</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45530.46568287037</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45925.54976851852</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45762</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>45182</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45389.3240162037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45567.66385416667</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45635.65060185185</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45926.34296296296</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45917.48241898148</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45926.66944444444</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45925.49892361111</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45252.38962962963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>44823.46959490741</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>45183.45549768519</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45588.56232638889</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>45602.4308912037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45028</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45705.63409722222</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>44825.28662037037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>45202.52186342593</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>44826</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>45771.53363425926</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45771.58298611111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45758</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44382.49001157407</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45331</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>44354.35270833333</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>45348.34381944445</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>44117</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>45160</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45677</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>45747.31387731482</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45090.3646875</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45744.30858796297</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>45705.39746527778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>44824</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>45329</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>45048.65945601852</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45586.49591435185</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45602.44824074074</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45758.52598379629</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44392.57740740741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>45749.9131712963</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>45173</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45447.87155092593</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45813.32416666667</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>45727</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45579</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44978.65341435185</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45155.42216435185</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45523.35789351852</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>45523.56410879629</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45733.65178240741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45258</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45175</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>45203</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>45530.48623842592</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45596.67273148148</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45317.41975694444</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45523.43003472222</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>45134</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45771</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45250</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45492.61072916666</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>44582.6703125</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45611.48383101852</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45771.683125</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45741</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45693</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45694.50859953704</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>45745.81983796296</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45695.59496527778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>45329</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44148</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>45757</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>45637.70347222222</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45072.61394675926</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45646.42331018519</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>45513</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>45386.55716435185</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45670.58081018519</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45625.66725694444</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45776.45123842593</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>45776.63219907408</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45776.44912037037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45777.45166666667</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45777</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>45777.44325231481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45486.57902777778</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45343</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45572.89640046296</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45783.43987268519</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>45404.62193287037</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>45092.68070601852</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>45187</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45758</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>44933.91175925926</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>45105</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>45470.47591435185</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>45181.57961805556</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45446.57864583333</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>44412</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36898,7 +36898,7 @@
         <v>45040</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>45533.36881944445</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>44873</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45223.61996527778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>45756.65042824074</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>44804</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45385.80540509259</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45478.55324074074</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45761.58778935186</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45761.59435185185</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45769.77425925926</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>45561.56449074074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45054</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45677.46194444445</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45751</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45751</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45533.38748842593</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45476</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45460.50371527778</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45523.55704861111</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>45371.36216435185</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>45531.58420138889</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45785</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>45350</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>44854.41751157407</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45034</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>45330</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45250</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>45250</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>45601.54574074074</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45335.54880787037</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>45448.47833333333</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>45791.53006944444</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38809,7 +38809,7 @@
         <v>45545.52954861111</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>45792</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45791.38825231481</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45792.43063657408</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>45363.29458333334</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>45791.38554398148</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45535</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>45113</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45791.56590277778</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45793.38363425926</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>45796.44629629629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>44466.44211805556</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>45274.67877314815</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45287.56077546296</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>45587.40817129629</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45537.61153935185</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44902.39201388889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45527.66319444445</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45558.56628472222</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44740.55820601852</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45084.57900462963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45560.59398148148</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45603.53090277778</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45531.42296296296</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45435</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45652.39298611111</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45798.66893518518</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45561.90840277778</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45635</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45798</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45798</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45560</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>45534.61678240741</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>45797</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>45314.61244212963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45394.56211805555</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>45535.42527777778</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>45800</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45723</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45800.63150462963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45803.62579861111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>45804.54371527778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>45800</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>45398.68</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45588.48271990741</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45744.57217592592</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45634.75663194444</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>45475.26847222223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45810.40319444444</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45807.565</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41739,7 +41739,7 @@
         <v>45810.57180555556</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45241.68520833334</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>44686.53328703704</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45807.57456018519</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>45593.43503472222</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>45810</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45553.53296296296</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>45553.54315972222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42215,7 +42215,7 @@
         <v>45398.54752314815</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45807.57137731482</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>45810.60783564814</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45174.55957175926</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45400.35174768518</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42500,7 +42500,7 @@
         <v>45175.65046296296</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>45429.61107638889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>45812.33471064815</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>45602.44324074074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45602.45038194444</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45811.39570601852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45173.94253472222</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>45611</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>45811.66383101852</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45811.66570601852</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>45597.63780092593</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45614.87096064815</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45618.55950231481</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45813</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45813.36081018519</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>45401.93005787037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>44995.44731481482</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45819</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45820</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45820.36541666667</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45820.38018518518</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45820.36188657407</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45820.35876157408</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45824.44313657407</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45824.54972222223</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>44558</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45659.58247685185</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45824.64821759259</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>45411.60905092592</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45825.55711805556</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>45825.34275462963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>45330.34628472223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>45329.50412037037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45825.591111